--- a/Development/Common/GameData/Monster.xlsx
+++ b/Development/Common/GameData/Monster.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\MMOGameServerProject\Common\GameData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\MMOGameServerProject\Development\Common\GameData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79C16105-F50B-40F5-802E-51BD96B04BEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65EC8864-3BE2-4314-A0F1-4FEF17CC0F16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="90">
   <si>
     <t>데이터이름</t>
   </si>
@@ -161,18 +161,10 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>HP</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>all</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>int</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>server</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -284,51 +276,79 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>None</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>스탯</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>적용할스탯 타입</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>적용할스탯 값</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>AddHP</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>AddMP</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>AddAtk</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>참고이름</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>테스</t>
-  </si>
-  <si>
-    <t>Co</t>
-  </si>
-  <si>
-    <t>Di</t>
-  </si>
-  <si>
-    <t>Re</t>
-  </si>
-  <si>
-    <t>Sc</t>
+    <t>기본 스탯</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stat4</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatValue4</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stat5</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatValue5</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stat6</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatValue6</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stat7</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatValue7</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stat8</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatValue8</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>StrAdd</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>IntAdd</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>MoveSpdAdd</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>HpAdd</t>
+  </si>
+  <si>
+    <t>MpAdd</t>
+  </si>
+  <si>
+    <t>PDefAdd</t>
+  </si>
+  <si>
+    <t>MDefAdd</t>
+  </si>
+  <si>
+    <t>AtkSpdAdd</t>
   </si>
 </sst>
 </file>
@@ -791,7 +811,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:Z21"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.25" style="12" customWidth="1"/>
@@ -799,21 +819,20 @@
     <col min="3" max="3" width="30.25" style="3" customWidth="1"/>
     <col min="4" max="4" width="26" style="3" customWidth="1"/>
     <col min="5" max="5" width="23.625" style="3" customWidth="1"/>
-    <col min="6" max="6" width="10.25" style="3" customWidth="1"/>
-    <col min="7" max="7" width="18.75" style="3" customWidth="1"/>
-    <col min="8" max="8" width="13.375" style="3" customWidth="1"/>
-    <col min="9" max="9" width="17.5" style="3" customWidth="1"/>
-    <col min="10" max="10" width="16.75" style="3" customWidth="1"/>
-    <col min="11" max="11" width="20.875" style="3" customWidth="1"/>
-    <col min="12" max="13" width="15.625" style="3" customWidth="1"/>
-    <col min="14" max="14" width="13.25" style="3" customWidth="1"/>
-    <col min="15" max="15" width="16.375" style="3" customWidth="1"/>
-    <col min="16" max="16" width="15.625" style="3" customWidth="1"/>
-    <col min="17" max="17" width="16.25" style="3" customWidth="1"/>
-    <col min="18" max="16384" width="9" style="3"/>
+    <col min="6" max="6" width="18.75" style="3" customWidth="1"/>
+    <col min="7" max="7" width="13.375" style="3" customWidth="1"/>
+    <col min="8" max="8" width="17.5" style="3" customWidth="1"/>
+    <col min="9" max="9" width="16.75" style="3" customWidth="1"/>
+    <col min="10" max="10" width="20.875" style="3" customWidth="1"/>
+    <col min="11" max="12" width="15.625" style="3" customWidth="1"/>
+    <col min="13" max="13" width="13.25" style="3" customWidth="1"/>
+    <col min="14" max="14" width="16.375" style="3" customWidth="1"/>
+    <col min="15" max="15" width="15.625" style="3" customWidth="1"/>
+    <col min="16" max="16" width="16.25" style="3" customWidth="1"/>
+    <col min="17" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -821,7 +840,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -838,29 +857,36 @@
         <v>38</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="J2" s="4"/>
+        <v>43</v>
+      </c>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4" t="s">
+        <v>57</v>
+      </c>
       <c r="K2" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>73</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="L2" s="4"/>
       <c r="M2" s="4"/>
       <c r="N2" s="4"/>
       <c r="O2" s="4"/>
       <c r="P2" s="4"/>
       <c r="Q2" s="4"/>
+      <c r="R2" s="4"/>
+      <c r="S2" s="4"/>
+      <c r="T2" s="4"/>
+      <c r="U2" s="4"/>
+      <c r="V2" s="4"/>
+      <c r="W2" s="4"/>
+      <c r="X2" s="4"/>
+      <c r="Y2" s="4"/>
+      <c r="Z2" s="4"/>
     </row>
-    <row r="3" spans="1:17" s="7" customFormat="1" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:26" s="7" customFormat="1" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
@@ -870,40 +896,37 @@
       <c r="E3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="6"/>
+      <c r="F3" s="6" t="s">
+        <v>45</v>
+      </c>
       <c r="G3" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>52</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="J3" s="6"/>
       <c r="K3" s="6"/>
-      <c r="L3" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="M3" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="N3" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="O3" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="P3" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q3" s="6" t="s">
-        <v>75</v>
-      </c>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6"/>
+      <c r="U3" s="6"/>
+      <c r="V3" s="6"/>
+      <c r="W3" s="6"/>
+      <c r="X3" s="6"/>
+      <c r="Y3" s="6"/>
+      <c r="Z3" s="6"/>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -923,40 +946,67 @@
         <v>42</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M4" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N4" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O4" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P4" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q4" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
+      </c>
+      <c r="R4" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="S4" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="T4" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="U4" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="V4" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="W4" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="X4" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y4" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z4" s="8" t="s">
+        <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -965,47 +1015,74 @@
       </c>
       <c r="C5" s="8"/>
       <c r="D5" s="8" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E5" s="8"/>
       <c r="F5" s="8" t="s">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="L5" s="8" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="M5" s="8" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="N5" s="8" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="O5" s="8" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="P5" s="8" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="Q5" s="8" t="s">
-        <v>64</v>
+        <v>54</v>
+      </c>
+      <c r="R5" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="S5" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="T5" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="U5" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="V5" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="W5" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="X5" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y5" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z5" s="8" t="s">
+        <v>62</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>35</v>
       </c>
@@ -1017,24 +1094,43 @@
       <c r="G6" s="8"/>
       <c r="H6" s="8"/>
       <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
+      <c r="J6" s="8" t="s">
+        <v>55</v>
+      </c>
       <c r="K6" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="L6" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="M6" s="8"/>
-      <c r="N6" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="O6" s="8"/>
-      <c r="P6" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="Q6" s="8"/>
+        <v>69</v>
+      </c>
+      <c r="L6" s="8"/>
+      <c r="M6" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="N6" s="8"/>
+      <c r="O6" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="P6" s="8"/>
+      <c r="Q6" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="R6" s="8"/>
+      <c r="S6" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="T6" s="8"/>
+      <c r="U6" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="V6" s="8"/>
+      <c r="W6" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="X6" s="8"/>
+      <c r="Y6" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z6" s="8"/>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
@@ -1045,43 +1141,54 @@
       <c r="D7" s="8"/>
       <c r="E7" s="8"/>
       <c r="F7" s="8">
-        <v>100</v>
-      </c>
-      <c r="G7" s="8">
         <v>0</v>
       </c>
-      <c r="H7" s="8" t="b">
+      <c r="G7" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="I7" s="8">
+      <c r="H7" s="8">
         <v>0</v>
       </c>
-      <c r="J7" s="8" t="b">
+      <c r="I7" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="K7" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="L7" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="M7" s="8">
+      <c r="J7" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8">
         <v>0</v>
       </c>
-      <c r="N7" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="O7" s="8">
+      <c r="M7" s="8"/>
+      <c r="N7" s="8">
         <v>0</v>
       </c>
-      <c r="P7" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q7" s="8">
+      <c r="O7" s="8"/>
+      <c r="P7" s="8">
         <v>0</v>
       </c>
+      <c r="Q7" s="8"/>
+      <c r="R7" s="8">
+        <v>0</v>
+      </c>
+      <c r="S7" s="8"/>
+      <c r="T7" s="8">
+        <v>0</v>
+      </c>
+      <c r="U7" s="8"/>
+      <c r="V7" s="8">
+        <v>0</v>
+      </c>
+      <c r="W7" s="8"/>
+      <c r="X7" s="8">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="8"/>
+      <c r="Z7" s="8">
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="1:17" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:26" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>14</v>
       </c>
@@ -1089,7 +1196,7 @@
         <v>15</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="D8" s="10" t="s">
         <v>39</v>
@@ -1098,43 +1205,70 @@
         <v>38</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H8" s="10" t="s">
         <v>51</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="L8" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="M8" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="N8" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="O8" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="M8" s="10" t="s">
+      <c r="P8" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="N8" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="O8" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="P8" s="10" t="s">
-        <v>67</v>
-      </c>
       <c r="Q8" s="10" t="s">
-        <v>70</v>
+        <v>72</v>
+      </c>
+      <c r="R8" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="S8" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="T8" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="U8" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="V8" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="W8" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="X8" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="Y8" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z8" s="10" t="s">
+        <v>81</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B9" s="3">
         <v>50</v>
       </c>
@@ -1145,31 +1279,64 @@
         <v>16</v>
       </c>
       <c r="F9" s="3">
-        <v>1000</v>
-      </c>
-      <c r="G9" s="3">
         <v>301</v>
       </c>
-      <c r="I9" s="3">
+      <c r="H9" s="3">
         <v>5.5</v>
       </c>
+      <c r="J9" s="3" t="s">
+        <v>59</v>
+      </c>
       <c r="K9" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="M9" s="3">
-        <v>100</v>
-      </c>
-      <c r="N9" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="O9" s="3">
-        <v>100</v>
+        <v>82</v>
+      </c>
+      <c r="L9" s="3">
+        <v>10</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="N9" s="3">
+        <v>10</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="P9" s="3">
+        <v>10</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="R9" s="3">
+        <v>100</v>
+      </c>
+      <c r="S9" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="T9" s="3">
+        <v>100</v>
+      </c>
+      <c r="U9" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="V9" s="3">
+        <v>10</v>
+      </c>
+      <c r="W9" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="X9" s="3">
+        <v>10</v>
+      </c>
+      <c r="Y9" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z9" s="3">
+        <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B10" s="3">
         <v>51</v>
       </c>
@@ -1180,31 +1347,64 @@
         <v>17</v>
       </c>
       <c r="F10" s="3">
-        <v>1000</v>
-      </c>
-      <c r="G10" s="3">
         <v>21</v>
       </c>
-      <c r="I10" s="3">
+      <c r="H10" s="3">
         <v>6.6</v>
       </c>
+      <c r="J10" s="3" t="s">
+        <v>59</v>
+      </c>
       <c r="K10" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="M10" s="3">
-        <v>200</v>
-      </c>
-      <c r="N10" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="O10" s="3">
-        <v>200</v>
+        <v>82</v>
+      </c>
+      <c r="L10" s="3">
+        <v>10</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="N10" s="3">
+        <v>10</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="P10" s="3">
+        <v>10</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="R10" s="3">
+        <v>100</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="T10" s="3">
+        <v>100</v>
+      </c>
+      <c r="U10" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="V10" s="3">
+        <v>10</v>
+      </c>
+      <c r="W10" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="X10" s="3">
+        <v>10</v>
+      </c>
+      <c r="Y10" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z10" s="3">
+        <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B11" s="3">
         <v>52</v>
       </c>
@@ -1215,31 +1415,64 @@
         <v>18</v>
       </c>
       <c r="F11" s="3">
-        <v>1000</v>
-      </c>
-      <c r="G11" s="3">
         <v>21</v>
       </c>
-      <c r="I11" s="3">
+      <c r="H11" s="3">
         <v>7.7</v>
       </c>
+      <c r="J11" s="3" t="s">
+        <v>59</v>
+      </c>
       <c r="K11" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="M11" s="3">
-        <v>100</v>
-      </c>
-      <c r="N11" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="O11" s="3">
-        <v>100</v>
+        <v>82</v>
+      </c>
+      <c r="L11" s="3">
+        <v>10</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="N11" s="3">
+        <v>10</v>
+      </c>
+      <c r="O11" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="P11" s="3">
+        <v>10</v>
+      </c>
+      <c r="Q11" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="R11" s="3">
+        <v>100</v>
+      </c>
+      <c r="S11" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="T11" s="3">
+        <v>100</v>
+      </c>
+      <c r="U11" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="V11" s="3">
+        <v>10</v>
+      </c>
+      <c r="W11" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="X11" s="3">
+        <v>10</v>
+      </c>
+      <c r="Y11" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z11" s="3">
+        <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B12" s="3">
         <v>53</v>
       </c>
@@ -1250,30 +1483,63 @@
         <v>19</v>
       </c>
       <c r="F12" s="3">
-        <v>1000</v>
-      </c>
-      <c r="G12" s="3">
         <v>21</v>
       </c>
-      <c r="I12" s="3">
+      <c r="H12" s="3">
         <v>8.8000000000000007</v>
       </c>
-      <c r="L12" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="M12" s="3">
-        <v>100</v>
-      </c>
-      <c r="P12" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>100</v>
+      <c r="K12" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="L12" s="3">
+        <v>10</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="N12" s="3">
+        <v>10</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="P12" s="3">
+        <v>10</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="R12" s="3">
+        <v>100</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="T12" s="3">
+        <v>100</v>
+      </c>
+      <c r="U12" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="V12" s="3">
+        <v>10</v>
+      </c>
+      <c r="W12" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="X12" s="3">
+        <v>10</v>
+      </c>
+      <c r="Y12" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z12" s="3">
+        <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A13" s="12" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B13" s="3">
         <v>54</v>
@@ -1285,31 +1551,64 @@
         <v>21</v>
       </c>
       <c r="F13" s="3">
-        <v>1000</v>
-      </c>
-      <c r="G13" s="3">
         <v>21</v>
       </c>
-      <c r="H13" s="3" t="b">
+      <c r="G13" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="I13" s="3">
+      <c r="H13" s="3">
         <v>9.9</v>
       </c>
-      <c r="L13" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="M13" s="3">
-        <v>200</v>
-      </c>
-      <c r="P13" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q13" s="3">
-        <v>100</v>
+      <c r="K13" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="L13" s="3">
+        <v>10</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="N13" s="3">
+        <v>10</v>
+      </c>
+      <c r="O13" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="P13" s="3">
+        <v>10</v>
+      </c>
+      <c r="Q13" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="R13" s="3">
+        <v>100</v>
+      </c>
+      <c r="S13" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="T13" s="3">
+        <v>100</v>
+      </c>
+      <c r="U13" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="V13" s="3">
+        <v>10</v>
+      </c>
+      <c r="W13" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="X13" s="3">
+        <v>10</v>
+      </c>
+      <c r="Y13" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z13" s="3">
+        <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B14" s="3">
         <v>55</v>
       </c>
@@ -1320,31 +1619,64 @@
         <v>23</v>
       </c>
       <c r="F14" s="3">
-        <v>1000</v>
-      </c>
-      <c r="G14" s="3">
         <v>201</v>
       </c>
-      <c r="I14" s="3">
+      <c r="H14" s="3">
         <v>11</v>
       </c>
+      <c r="J14" s="3" t="s">
+        <v>60</v>
+      </c>
       <c r="K14" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="M14" s="3">
-        <v>100</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>100</v>
+        <v>82</v>
+      </c>
+      <c r="L14" s="3">
+        <v>10</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="N14" s="3">
+        <v>10</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="P14" s="3">
+        <v>10</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="R14" s="3">
+        <v>100</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="T14" s="3">
+        <v>100</v>
+      </c>
+      <c r="U14" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="V14" s="3">
+        <v>10</v>
+      </c>
+      <c r="W14" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="X14" s="3">
+        <v>10</v>
+      </c>
+      <c r="Y14" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z14" s="3">
+        <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B15" s="3">
         <v>56</v>
       </c>
@@ -1355,40 +1687,67 @@
         <v>25</v>
       </c>
       <c r="F15" s="3">
-        <v>1000</v>
-      </c>
-      <c r="G15" s="3">
         <v>301</v>
       </c>
-      <c r="I15" s="3">
+      <c r="H15" s="3">
         <v>12.1</v>
       </c>
-      <c r="J15" s="3" t="b">
+      <c r="I15" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="J15" s="3" t="s">
+        <v>60</v>
+      </c>
       <c r="K15" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="M15" s="3">
-        <v>100</v>
-      </c>
-      <c r="N15" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="O15" s="3">
-        <v>100</v>
-      </c>
-      <c r="P15" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>200</v>
+        <v>82</v>
+      </c>
+      <c r="L15" s="3">
+        <v>10</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="N15" s="3">
+        <v>10</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="P15" s="3">
+        <v>10</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="R15" s="3">
+        <v>100</v>
+      </c>
+      <c r="S15" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="T15" s="3">
+        <v>100</v>
+      </c>
+      <c r="U15" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="V15" s="3">
+        <v>10</v>
+      </c>
+      <c r="W15" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="X15" s="3">
+        <v>10</v>
+      </c>
+      <c r="Y15" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z15" s="3">
+        <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B16" s="3">
         <v>60</v>
       </c>
@@ -1399,40 +1758,67 @@
         <v>27</v>
       </c>
       <c r="F16" s="3">
-        <v>1000</v>
-      </c>
-      <c r="G16" s="3">
         <v>301</v>
       </c>
-      <c r="I16" s="3">
+      <c r="H16" s="3">
         <v>13.2</v>
       </c>
-      <c r="J16" s="3" t="b">
+      <c r="I16" s="3" t="b">
         <v>0</v>
       </c>
+      <c r="J16" s="3" t="s">
+        <v>60</v>
+      </c>
       <c r="K16" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="L16" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="M16" s="3">
-        <v>200</v>
-      </c>
-      <c r="N16" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="O16" s="3">
-        <v>200</v>
-      </c>
-      <c r="P16" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q16" s="3">
-        <v>100</v>
+        <v>82</v>
+      </c>
+      <c r="L16" s="3">
+        <v>10</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="N16" s="3">
+        <v>10</v>
+      </c>
+      <c r="O16" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="P16" s="3">
+        <v>10</v>
+      </c>
+      <c r="Q16" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="R16" s="3">
+        <v>100</v>
+      </c>
+      <c r="S16" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="T16" s="3">
+        <v>100</v>
+      </c>
+      <c r="U16" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="V16" s="3">
+        <v>10</v>
+      </c>
+      <c r="W16" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="X16" s="3">
+        <v>10</v>
+      </c>
+      <c r="Y16" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z16" s="3">
+        <v>1</v>
       </c>
     </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B17" s="3">
         <v>91</v>
       </c>
@@ -1443,31 +1829,64 @@
         <v>29</v>
       </c>
       <c r="F17" s="3">
-        <v>1000</v>
-      </c>
-      <c r="G17" s="3">
         <v>99</v>
       </c>
-      <c r="I17" s="3">
+      <c r="H17" s="3">
         <v>14.3</v>
       </c>
+      <c r="J17" s="3" t="s">
+        <v>60</v>
+      </c>
       <c r="K17" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="L17" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="M17" s="3">
-        <v>100</v>
-      </c>
-      <c r="N17" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="O17" s="3">
-        <v>100</v>
+        <v>82</v>
+      </c>
+      <c r="L17" s="3">
+        <v>10</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="N17" s="3">
+        <v>10</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="P17" s="3">
+        <v>10</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="R17" s="3">
+        <v>100</v>
+      </c>
+      <c r="S17" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="T17" s="3">
+        <v>100</v>
+      </c>
+      <c r="U17" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="V17" s="3">
+        <v>10</v>
+      </c>
+      <c r="W17" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="X17" s="3">
+        <v>10</v>
+      </c>
+      <c r="Y17" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z17" s="3">
+        <v>1</v>
       </c>
     </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B18" s="3">
         <v>97</v>
       </c>
@@ -1478,25 +1897,64 @@
         <v>31</v>
       </c>
       <c r="F18" s="3">
-        <v>1000</v>
-      </c>
-      <c r="G18" s="3">
         <v>99</v>
       </c>
-      <c r="I18" s="3">
+      <c r="H18" s="3">
         <v>15.4</v>
       </c>
+      <c r="J18" s="3" t="s">
+        <v>61</v>
+      </c>
       <c r="K18" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="M18" s="3">
-        <v>100</v>
+        <v>82</v>
+      </c>
+      <c r="L18" s="3">
+        <v>10</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="N18" s="3">
+        <v>10</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="P18" s="3">
+        <v>10</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="R18" s="3">
+        <v>100</v>
+      </c>
+      <c r="S18" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="T18" s="3">
+        <v>100</v>
+      </c>
+      <c r="U18" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="V18" s="3">
+        <v>10</v>
+      </c>
+      <c r="W18" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="X18" s="3">
+        <v>10</v>
+      </c>
+      <c r="Y18" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z18" s="3">
+        <v>1</v>
       </c>
     </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B19" s="3">
         <v>98</v>
       </c>
@@ -1507,19 +1965,64 @@
         <v>33</v>
       </c>
       <c r="F19" s="3">
-        <v>1000</v>
-      </c>
-      <c r="G19" s="3">
         <v>99</v>
       </c>
-      <c r="I19" s="3">
+      <c r="H19" s="3">
         <v>16.5</v>
       </c>
+      <c r="J19" s="3" t="s">
+        <v>61</v>
+      </c>
       <c r="K19" s="3" t="s">
-        <v>63</v>
+        <v>82</v>
+      </c>
+      <c r="L19" s="3">
+        <v>10</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="N19" s="3">
+        <v>10</v>
+      </c>
+      <c r="O19" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="P19" s="3">
+        <v>10</v>
+      </c>
+      <c r="Q19" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="R19" s="3">
+        <v>100</v>
+      </c>
+      <c r="S19" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="T19" s="3">
+        <v>100</v>
+      </c>
+      <c r="U19" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="V19" s="3">
+        <v>10</v>
+      </c>
+      <c r="W19" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="X19" s="3">
+        <v>10</v>
+      </c>
+      <c r="Y19" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z19" s="3">
+        <v>1</v>
       </c>
     </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B20" s="3">
         <v>99</v>
       </c>
@@ -1530,19 +2033,64 @@
         <v>33</v>
       </c>
       <c r="F20" s="3">
-        <v>1000</v>
-      </c>
-      <c r="G20" s="3">
         <v>99</v>
       </c>
-      <c r="I20" s="3">
+      <c r="H20" s="3">
         <v>17.600000000000001</v>
       </c>
+      <c r="J20" s="3" t="s">
+        <v>61</v>
+      </c>
       <c r="K20" s="3" t="s">
-        <v>63</v>
+        <v>82</v>
+      </c>
+      <c r="L20" s="3">
+        <v>10</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="N20" s="3">
+        <v>10</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="P20" s="3">
+        <v>10</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="R20" s="3">
+        <v>100</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="T20" s="3">
+        <v>100</v>
+      </c>
+      <c r="U20" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="V20" s="3">
+        <v>10</v>
+      </c>
+      <c r="W20" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="X20" s="3">
+        <v>10</v>
+      </c>
+      <c r="Y20" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z20" s="3">
+        <v>1</v>
       </c>
     </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B21" s="3">
         <v>100</v>
       </c>
@@ -1553,16 +2101,61 @@
         <v>34</v>
       </c>
       <c r="F21" s="3">
-        <v>1000</v>
-      </c>
-      <c r="G21" s="3">
         <v>20</v>
       </c>
-      <c r="I21" s="3">
+      <c r="H21" s="3">
         <v>18.7</v>
       </c>
+      <c r="J21" s="3" t="s">
+        <v>61</v>
+      </c>
       <c r="K21" s="3" t="s">
-        <v>63</v>
+        <v>82</v>
+      </c>
+      <c r="L21" s="3">
+        <v>10</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="N21" s="3">
+        <v>10</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="P21" s="3">
+        <v>10</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="R21" s="3">
+        <v>100</v>
+      </c>
+      <c r="S21" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="T21" s="3">
+        <v>100</v>
+      </c>
+      <c r="U21" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="V21" s="3">
+        <v>10</v>
+      </c>
+      <c r="W21" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="X21" s="3">
+        <v>10</v>
+      </c>
+      <c r="Y21" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z21" s="3">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Development/Common/GameData/Monster.xlsx
+++ b/Development/Common/GameData/Monster.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\MMOGameServerProject\Development\Common\GameData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B533F9C-BCA3-4232-9C3F-F013E30D96A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B7C2637-BAF7-435B-948D-2966D81C4C96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3495" yWindow="3585" windowWidth="31605" windowHeight="17295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Monster" sheetId="1" r:id="rId1"/>
@@ -73,9 +73,6 @@
     <t>DataType</t>
   </si>
   <si>
-    <t>int</t>
-  </si>
-  <si>
     <t>DefaultValue</t>
   </si>
   <si>
@@ -456,6 +453,10 @@
   </si>
   <si>
     <t>Prefabs/Monsters/Slime_03 Sprout_big</t>
+  </si>
+  <si>
+    <t>int32</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -956,30 +957,30 @@
         <v>3</v>
       </c>
       <c r="C2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>18</v>
-      </c>
       <c r="F2" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H2" s="4"/>
       <c r="I2" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J2" s="4"/>
       <c r="K2" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="M2" s="4"/>
       <c r="N2" s="4"/>
@@ -1005,22 +1006,22 @@
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
       <c r="E3" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G3" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" s="6" t="s">
         <v>25</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>26</v>
       </c>
       <c r="I3" s="6" t="s">
         <v>5</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K3" s="6"/>
       <c r="L3" s="6"/>
@@ -1051,76 +1052,76 @@
         <v>8</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E4" s="8" t="s">
         <v>8</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H4" s="8" t="s">
         <v>9</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M4" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N4" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="O4" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P4" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q4" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R4" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S4" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="T4" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="U4" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V4" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="W4" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="X4" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y4" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Z4" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA4" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.3">
@@ -1128,83 +1129,83 @@
         <v>10</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>11</v>
+        <v>118</v>
       </c>
       <c r="C5" s="8"/>
       <c r="D5" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E5" s="8"/>
       <c r="F5" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="K5" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="G5" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="J5" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="K5" s="8" t="s">
-        <v>34</v>
-      </c>
       <c r="L5" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M5" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N5" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O5" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P5" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q5" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="R5" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="S5" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="T5" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="U5" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V5" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="W5" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="X5" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Y5" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Z5" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="AA5" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -1216,44 +1217,44 @@
       <c r="I6" s="8"/>
       <c r="J6" s="8"/>
       <c r="K6" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L6" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M6" s="8"/>
       <c r="N6" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O6" s="8"/>
       <c r="P6" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Q6" s="8"/>
       <c r="R6" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="S6" s="8"/>
       <c r="T6" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="U6" s="8"/>
       <c r="V6" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="W6" s="8"/>
       <c r="X6" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Y6" s="8"/>
       <c r="Z6" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AA6" s="8"/>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B7" s="8">
         <v>0</v>
@@ -1275,7 +1276,7 @@
         <v>1</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L7" s="8"/>
       <c r="M7" s="8">
@@ -1312,85 +1313,85 @@
     </row>
     <row r="8" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="10" t="s">
-        <v>14</v>
-      </c>
       <c r="C8" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I8" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="J8" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="J8" s="10" t="s">
-        <v>32</v>
-      </c>
       <c r="K8" s="10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L8" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="M8" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="N8" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="M8" s="10" t="s">
+      <c r="O8" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="N8" s="10" t="s">
+      <c r="P8" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="O8" s="10" t="s">
+      <c r="Q8" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="P8" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q8" s="10" t="s">
-        <v>45</v>
-      </c>
       <c r="R8" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="S8" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="S8" s="10" t="s">
+      <c r="T8" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="T8" s="10" t="s">
+      <c r="U8" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="U8" s="10" t="s">
+      <c r="V8" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="V8" s="10" t="s">
+      <c r="W8" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="W8" s="10" t="s">
+      <c r="X8" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="X8" s="10" t="s">
+      <c r="Y8" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="Y8" s="10" t="s">
+      <c r="Z8" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="Z8" s="10" t="s">
+      <c r="AA8" s="10" t="s">
         <v>57</v>
-      </c>
-      <c r="AA8" s="10" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.3">
@@ -1398,13 +1399,13 @@
         <v>50</v>
       </c>
       <c r="C9" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>85</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>86</v>
       </c>
       <c r="G9" s="3">
         <v>301</v>
@@ -1413,52 +1414,52 @@
         <v>5.5</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L9" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="M9" s="3">
+        <v>10</v>
+      </c>
+      <c r="N9" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="M9" s="3">
-        <v>10</v>
-      </c>
-      <c r="N9" s="3" t="s">
+      <c r="O9" s="3">
+        <v>10</v>
+      </c>
+      <c r="P9" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="O9" s="3">
-        <v>10</v>
-      </c>
-      <c r="P9" s="3" t="s">
+      <c r="Q9" s="3">
+        <v>10</v>
+      </c>
+      <c r="R9" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="Q9" s="3">
-        <v>10</v>
-      </c>
-      <c r="R9" s="3" t="s">
+      <c r="S9" s="3">
+        <v>100</v>
+      </c>
+      <c r="T9" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="S9" s="3">
-        <v>100</v>
-      </c>
-      <c r="T9" s="3" t="s">
+      <c r="U9" s="3">
+        <v>100</v>
+      </c>
+      <c r="V9" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="U9" s="3">
-        <v>100</v>
-      </c>
-      <c r="V9" s="3" t="s">
+      <c r="W9" s="3">
+        <v>10</v>
+      </c>
+      <c r="X9" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="W9" s="3">
-        <v>10</v>
-      </c>
-      <c r="X9" s="3" t="s">
+      <c r="Y9" s="3">
+        <v>10</v>
+      </c>
+      <c r="Z9" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="Y9" s="3">
-        <v>10</v>
-      </c>
-      <c r="Z9" s="3" t="s">
-        <v>66</v>
       </c>
       <c r="AA9" s="3">
         <v>1</v>
@@ -1469,13 +1470,13 @@
         <v>51</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G10" s="3">
         <v>21</v>
@@ -1484,52 +1485,52 @@
         <v>6.6</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L10" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="M10" s="3">
+        <v>10</v>
+      </c>
+      <c r="N10" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="M10" s="3">
-        <v>10</v>
-      </c>
-      <c r="N10" s="3" t="s">
+      <c r="O10" s="3">
+        <v>10</v>
+      </c>
+      <c r="P10" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="O10" s="3">
-        <v>10</v>
-      </c>
-      <c r="P10" s="3" t="s">
+      <c r="Q10" s="3">
+        <v>10</v>
+      </c>
+      <c r="R10" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="Q10" s="3">
-        <v>10</v>
-      </c>
-      <c r="R10" s="3" t="s">
+      <c r="S10" s="3">
+        <v>100</v>
+      </c>
+      <c r="T10" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="S10" s="3">
-        <v>100</v>
-      </c>
-      <c r="T10" s="3" t="s">
+      <c r="U10" s="3">
+        <v>100</v>
+      </c>
+      <c r="V10" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="U10" s="3">
-        <v>100</v>
-      </c>
-      <c r="V10" s="3" t="s">
+      <c r="W10" s="3">
+        <v>10</v>
+      </c>
+      <c r="X10" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="W10" s="3">
-        <v>10</v>
-      </c>
-      <c r="X10" s="3" t="s">
+      <c r="Y10" s="3">
+        <v>10</v>
+      </c>
+      <c r="Z10" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="Y10" s="3">
-        <v>10</v>
-      </c>
-      <c r="Z10" s="3" t="s">
-        <v>66</v>
       </c>
       <c r="AA10" s="3">
         <v>1</v>
@@ -1540,13 +1541,13 @@
         <v>52</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G11" s="3">
         <v>21</v>
@@ -1555,52 +1556,52 @@
         <v>7.7</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L11" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="M11" s="3">
+        <v>10</v>
+      </c>
+      <c r="N11" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="M11" s="3">
-        <v>10</v>
-      </c>
-      <c r="N11" s="3" t="s">
+      <c r="O11" s="3">
+        <v>10</v>
+      </c>
+      <c r="P11" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="O11" s="3">
-        <v>10</v>
-      </c>
-      <c r="P11" s="3" t="s">
+      <c r="Q11" s="3">
+        <v>10</v>
+      </c>
+      <c r="R11" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="Q11" s="3">
-        <v>10</v>
-      </c>
-      <c r="R11" s="3" t="s">
+      <c r="S11" s="3">
+        <v>100</v>
+      </c>
+      <c r="T11" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="S11" s="3">
-        <v>100</v>
-      </c>
-      <c r="T11" s="3" t="s">
+      <c r="U11" s="3">
+        <v>100</v>
+      </c>
+      <c r="V11" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="U11" s="3">
-        <v>100</v>
-      </c>
-      <c r="V11" s="3" t="s">
+      <c r="W11" s="3">
+        <v>10</v>
+      </c>
+      <c r="X11" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="W11" s="3">
-        <v>10</v>
-      </c>
-      <c r="X11" s="3" t="s">
+      <c r="Y11" s="3">
+        <v>10</v>
+      </c>
+      <c r="Z11" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="Y11" s="3">
-        <v>10</v>
-      </c>
-      <c r="Z11" s="3" t="s">
-        <v>66</v>
       </c>
       <c r="AA11" s="3">
         <v>1</v>
@@ -1611,13 +1612,13 @@
         <v>53</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G12" s="3">
         <v>301</v>
@@ -1626,52 +1627,52 @@
         <v>5.5</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L12" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="M12" s="3">
+        <v>10</v>
+      </c>
+      <c r="N12" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="M12" s="3">
-        <v>10</v>
-      </c>
-      <c r="N12" s="3" t="s">
+      <c r="O12" s="3">
+        <v>10</v>
+      </c>
+      <c r="P12" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="O12" s="3">
-        <v>10</v>
-      </c>
-      <c r="P12" s="3" t="s">
+      <c r="Q12" s="3">
+        <v>10</v>
+      </c>
+      <c r="R12" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="Q12" s="3">
-        <v>10</v>
-      </c>
-      <c r="R12" s="3" t="s">
+      <c r="S12" s="3">
+        <v>100</v>
+      </c>
+      <c r="T12" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="S12" s="3">
-        <v>100</v>
-      </c>
-      <c r="T12" s="3" t="s">
+      <c r="U12" s="3">
+        <v>100</v>
+      </c>
+      <c r="V12" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="U12" s="3">
-        <v>100</v>
-      </c>
-      <c r="V12" s="3" t="s">
+      <c r="W12" s="3">
+        <v>10</v>
+      </c>
+      <c r="X12" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="W12" s="3">
-        <v>10</v>
-      </c>
-      <c r="X12" s="3" t="s">
+      <c r="Y12" s="3">
+        <v>10</v>
+      </c>
+      <c r="Z12" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="Y12" s="3">
-        <v>10</v>
-      </c>
-      <c r="Z12" s="3" t="s">
-        <v>66</v>
       </c>
       <c r="AA12" s="3">
         <v>1</v>
@@ -1682,13 +1683,13 @@
         <v>54</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G13" s="3">
         <v>21</v>
@@ -1697,52 +1698,52 @@
         <v>6.6</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L13" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="M13" s="3">
+        <v>10</v>
+      </c>
+      <c r="N13" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="M13" s="3">
-        <v>10</v>
-      </c>
-      <c r="N13" s="3" t="s">
+      <c r="O13" s="3">
+        <v>10</v>
+      </c>
+      <c r="P13" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="O13" s="3">
-        <v>10</v>
-      </c>
-      <c r="P13" s="3" t="s">
+      <c r="Q13" s="3">
+        <v>10</v>
+      </c>
+      <c r="R13" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="Q13" s="3">
-        <v>10</v>
-      </c>
-      <c r="R13" s="3" t="s">
+      <c r="S13" s="3">
+        <v>100</v>
+      </c>
+      <c r="T13" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="S13" s="3">
-        <v>100</v>
-      </c>
-      <c r="T13" s="3" t="s">
+      <c r="U13" s="3">
+        <v>100</v>
+      </c>
+      <c r="V13" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="U13" s="3">
-        <v>100</v>
-      </c>
-      <c r="V13" s="3" t="s">
+      <c r="W13" s="3">
+        <v>10</v>
+      </c>
+      <c r="X13" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="W13" s="3">
-        <v>10</v>
-      </c>
-      <c r="X13" s="3" t="s">
+      <c r="Y13" s="3">
+        <v>10</v>
+      </c>
+      <c r="Z13" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="Y13" s="3">
-        <v>10</v>
-      </c>
-      <c r="Z13" s="3" t="s">
-        <v>66</v>
       </c>
       <c r="AA13" s="3">
         <v>1</v>
@@ -1753,13 +1754,13 @@
         <v>55</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G14" s="3">
         <v>21</v>
@@ -1768,52 +1769,52 @@
         <v>7.7</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L14" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="M14" s="3">
+        <v>10</v>
+      </c>
+      <c r="N14" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="M14" s="3">
-        <v>10</v>
-      </c>
-      <c r="N14" s="3" t="s">
+      <c r="O14" s="3">
+        <v>10</v>
+      </c>
+      <c r="P14" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="O14" s="3">
-        <v>10</v>
-      </c>
-      <c r="P14" s="3" t="s">
+      <c r="Q14" s="3">
+        <v>10</v>
+      </c>
+      <c r="R14" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="Q14" s="3">
-        <v>10</v>
-      </c>
-      <c r="R14" s="3" t="s">
+      <c r="S14" s="3">
+        <v>100</v>
+      </c>
+      <c r="T14" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="S14" s="3">
-        <v>100</v>
-      </c>
-      <c r="T14" s="3" t="s">
+      <c r="U14" s="3">
+        <v>100</v>
+      </c>
+      <c r="V14" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="U14" s="3">
-        <v>100</v>
-      </c>
-      <c r="V14" s="3" t="s">
+      <c r="W14" s="3">
+        <v>10</v>
+      </c>
+      <c r="X14" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="W14" s="3">
-        <v>10</v>
-      </c>
-      <c r="X14" s="3" t="s">
+      <c r="Y14" s="3">
+        <v>10</v>
+      </c>
+      <c r="Z14" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="Y14" s="3">
-        <v>10</v>
-      </c>
-      <c r="Z14" s="3" t="s">
-        <v>66</v>
       </c>
       <c r="AA14" s="3">
         <v>1</v>
@@ -1824,13 +1825,13 @@
         <v>56</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G15" s="3">
         <v>301</v>
@@ -1839,52 +1840,52 @@
         <v>5.5</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L15" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="M15" s="3">
+        <v>10</v>
+      </c>
+      <c r="N15" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="M15" s="3">
-        <v>10</v>
-      </c>
-      <c r="N15" s="3" t="s">
+      <c r="O15" s="3">
+        <v>10</v>
+      </c>
+      <c r="P15" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="O15" s="3">
-        <v>10</v>
-      </c>
-      <c r="P15" s="3" t="s">
+      <c r="Q15" s="3">
+        <v>10</v>
+      </c>
+      <c r="R15" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="Q15" s="3">
-        <v>10</v>
-      </c>
-      <c r="R15" s="3" t="s">
+      <c r="S15" s="3">
+        <v>100</v>
+      </c>
+      <c r="T15" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="S15" s="3">
-        <v>100</v>
-      </c>
-      <c r="T15" s="3" t="s">
+      <c r="U15" s="3">
+        <v>100</v>
+      </c>
+      <c r="V15" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="U15" s="3">
-        <v>100</v>
-      </c>
-      <c r="V15" s="3" t="s">
+      <c r="W15" s="3">
+        <v>10</v>
+      </c>
+      <c r="X15" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="W15" s="3">
-        <v>10</v>
-      </c>
-      <c r="X15" s="3" t="s">
+      <c r="Y15" s="3">
+        <v>10</v>
+      </c>
+      <c r="Z15" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="Y15" s="3">
-        <v>10</v>
-      </c>
-      <c r="Z15" s="3" t="s">
-        <v>66</v>
       </c>
       <c r="AA15" s="3">
         <v>1</v>
@@ -1895,13 +1896,13 @@
         <v>57</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G16" s="3">
         <v>21</v>
@@ -1910,52 +1911,52 @@
         <v>6.6</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L16" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="M16" s="3">
+        <v>10</v>
+      </c>
+      <c r="N16" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="M16" s="3">
-        <v>10</v>
-      </c>
-      <c r="N16" s="3" t="s">
+      <c r="O16" s="3">
+        <v>10</v>
+      </c>
+      <c r="P16" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="O16" s="3">
-        <v>10</v>
-      </c>
-      <c r="P16" s="3" t="s">
+      <c r="Q16" s="3">
+        <v>10</v>
+      </c>
+      <c r="R16" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="Q16" s="3">
-        <v>10</v>
-      </c>
-      <c r="R16" s="3" t="s">
+      <c r="S16" s="3">
+        <v>100</v>
+      </c>
+      <c r="T16" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="S16" s="3">
-        <v>100</v>
-      </c>
-      <c r="T16" s="3" t="s">
+      <c r="U16" s="3">
+        <v>100</v>
+      </c>
+      <c r="V16" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="U16" s="3">
-        <v>100</v>
-      </c>
-      <c r="V16" s="3" t="s">
+      <c r="W16" s="3">
+        <v>10</v>
+      </c>
+      <c r="X16" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="W16" s="3">
-        <v>10</v>
-      </c>
-      <c r="X16" s="3" t="s">
+      <c r="Y16" s="3">
+        <v>10</v>
+      </c>
+      <c r="Z16" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="Y16" s="3">
-        <v>10</v>
-      </c>
-      <c r="Z16" s="3" t="s">
-        <v>66</v>
       </c>
       <c r="AA16" s="3">
         <v>1</v>
@@ -1966,13 +1967,13 @@
         <v>58</v>
       </c>
       <c r="C17" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>84</v>
-      </c>
       <c r="F17" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G17" s="3">
         <v>21</v>
@@ -1981,52 +1982,52 @@
         <v>7.7</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L17" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="M17" s="3">
+        <v>10</v>
+      </c>
+      <c r="N17" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="M17" s="3">
-        <v>10</v>
-      </c>
-      <c r="N17" s="3" t="s">
+      <c r="O17" s="3">
+        <v>10</v>
+      </c>
+      <c r="P17" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="O17" s="3">
-        <v>10</v>
-      </c>
-      <c r="P17" s="3" t="s">
+      <c r="Q17" s="3">
+        <v>10</v>
+      </c>
+      <c r="R17" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="Q17" s="3">
-        <v>10</v>
-      </c>
-      <c r="R17" s="3" t="s">
+      <c r="S17" s="3">
+        <v>100</v>
+      </c>
+      <c r="T17" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="S17" s="3">
-        <v>100</v>
-      </c>
-      <c r="T17" s="3" t="s">
+      <c r="U17" s="3">
+        <v>100</v>
+      </c>
+      <c r="V17" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="U17" s="3">
-        <v>100</v>
-      </c>
-      <c r="V17" s="3" t="s">
+      <c r="W17" s="3">
+        <v>10</v>
+      </c>
+      <c r="X17" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="W17" s="3">
-        <v>10</v>
-      </c>
-      <c r="X17" s="3" t="s">
+      <c r="Y17" s="3">
+        <v>10</v>
+      </c>
+      <c r="Z17" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="Y17" s="3">
-        <v>10</v>
-      </c>
-      <c r="Z17" s="3" t="s">
-        <v>66</v>
       </c>
       <c r="AA17" s="3">
         <v>1</v>
@@ -2037,13 +2038,13 @@
         <v>59</v>
       </c>
       <c r="C18" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="F18" s="3" t="s">
         <v>96</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>97</v>
       </c>
       <c r="G18" s="3">
         <v>301</v>
@@ -2052,52 +2053,52 @@
         <v>5.5</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L18" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="M18" s="3">
+        <v>10</v>
+      </c>
+      <c r="N18" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="M18" s="3">
-        <v>10</v>
-      </c>
-      <c r="N18" s="3" t="s">
+      <c r="O18" s="3">
+        <v>10</v>
+      </c>
+      <c r="P18" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="O18" s="3">
-        <v>10</v>
-      </c>
-      <c r="P18" s="3" t="s">
+      <c r="Q18" s="3">
+        <v>10</v>
+      </c>
+      <c r="R18" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="Q18" s="3">
-        <v>10</v>
-      </c>
-      <c r="R18" s="3" t="s">
+      <c r="S18" s="3">
+        <v>100</v>
+      </c>
+      <c r="T18" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="S18" s="3">
-        <v>100</v>
-      </c>
-      <c r="T18" s="3" t="s">
+      <c r="U18" s="3">
+        <v>100</v>
+      </c>
+      <c r="V18" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="U18" s="3">
-        <v>100</v>
-      </c>
-      <c r="V18" s="3" t="s">
+      <c r="W18" s="3">
+        <v>10</v>
+      </c>
+      <c r="X18" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="W18" s="3">
-        <v>10</v>
-      </c>
-      <c r="X18" s="3" t="s">
+      <c r="Y18" s="3">
+        <v>10</v>
+      </c>
+      <c r="Z18" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="Y18" s="3">
-        <v>10</v>
-      </c>
-      <c r="Z18" s="3" t="s">
-        <v>66</v>
       </c>
       <c r="AA18" s="3">
         <v>1</v>
@@ -2108,13 +2109,13 @@
         <v>60</v>
       </c>
       <c r="C19" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="F19" s="3" t="s">
         <v>99</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>100</v>
       </c>
       <c r="G19" s="3">
         <v>21</v>
@@ -2123,52 +2124,52 @@
         <v>6.6</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L19" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="M19" s="3">
+        <v>10</v>
+      </c>
+      <c r="N19" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="M19" s="3">
-        <v>10</v>
-      </c>
-      <c r="N19" s="3" t="s">
+      <c r="O19" s="3">
+        <v>10</v>
+      </c>
+      <c r="P19" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="O19" s="3">
-        <v>10</v>
-      </c>
-      <c r="P19" s="3" t="s">
+      <c r="Q19" s="3">
+        <v>10</v>
+      </c>
+      <c r="R19" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="Q19" s="3">
-        <v>10</v>
-      </c>
-      <c r="R19" s="3" t="s">
+      <c r="S19" s="3">
+        <v>100</v>
+      </c>
+      <c r="T19" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="S19" s="3">
-        <v>100</v>
-      </c>
-      <c r="T19" s="3" t="s">
+      <c r="U19" s="3">
+        <v>100</v>
+      </c>
+      <c r="V19" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="U19" s="3">
-        <v>100</v>
-      </c>
-      <c r="V19" s="3" t="s">
+      <c r="W19" s="3">
+        <v>10</v>
+      </c>
+      <c r="X19" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="W19" s="3">
-        <v>10</v>
-      </c>
-      <c r="X19" s="3" t="s">
+      <c r="Y19" s="3">
+        <v>10</v>
+      </c>
+      <c r="Z19" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="Y19" s="3">
-        <v>10</v>
-      </c>
-      <c r="Z19" s="3" t="s">
-        <v>66</v>
       </c>
       <c r="AA19" s="3">
         <v>1</v>
@@ -2179,13 +2180,13 @@
         <v>61</v>
       </c>
       <c r="C20" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="F20" s="3" t="s">
         <v>102</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>103</v>
       </c>
       <c r="G20" s="3">
         <v>21</v>
@@ -2194,52 +2195,52 @@
         <v>7.7</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L20" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="M20" s="3">
+        <v>10</v>
+      </c>
+      <c r="N20" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="M20" s="3">
-        <v>10</v>
-      </c>
-      <c r="N20" s="3" t="s">
+      <c r="O20" s="3">
+        <v>10</v>
+      </c>
+      <c r="P20" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="O20" s="3">
-        <v>10</v>
-      </c>
-      <c r="P20" s="3" t="s">
+      <c r="Q20" s="3">
+        <v>10</v>
+      </c>
+      <c r="R20" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="Q20" s="3">
-        <v>10</v>
-      </c>
-      <c r="R20" s="3" t="s">
+      <c r="S20" s="3">
+        <v>100</v>
+      </c>
+      <c r="T20" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="S20" s="3">
-        <v>100</v>
-      </c>
-      <c r="T20" s="3" t="s">
+      <c r="U20" s="3">
+        <v>100</v>
+      </c>
+      <c r="V20" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="U20" s="3">
-        <v>100</v>
-      </c>
-      <c r="V20" s="3" t="s">
+      <c r="W20" s="3">
+        <v>10</v>
+      </c>
+      <c r="X20" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="W20" s="3">
-        <v>10</v>
-      </c>
-      <c r="X20" s="3" t="s">
+      <c r="Y20" s="3">
+        <v>10</v>
+      </c>
+      <c r="Z20" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>10</v>
-      </c>
-      <c r="Z20" s="3" t="s">
-        <v>66</v>
       </c>
       <c r="AA20" s="3">
         <v>1</v>
@@ -2250,13 +2251,13 @@
         <v>62</v>
       </c>
       <c r="C21" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D21" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="F21" s="3" t="s">
         <v>105</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>106</v>
       </c>
       <c r="G21" s="3">
         <v>301</v>
@@ -2265,52 +2266,52 @@
         <v>5.5</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L21" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="M21" s="3">
+        <v>10</v>
+      </c>
+      <c r="N21" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="M21" s="3">
-        <v>10</v>
-      </c>
-      <c r="N21" s="3" t="s">
+      <c r="O21" s="3">
+        <v>10</v>
+      </c>
+      <c r="P21" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="O21" s="3">
-        <v>10</v>
-      </c>
-      <c r="P21" s="3" t="s">
+      <c r="Q21" s="3">
+        <v>10</v>
+      </c>
+      <c r="R21" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="Q21" s="3">
-        <v>10</v>
-      </c>
-      <c r="R21" s="3" t="s">
+      <c r="S21" s="3">
+        <v>100</v>
+      </c>
+      <c r="T21" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="S21" s="3">
-        <v>100</v>
-      </c>
-      <c r="T21" s="3" t="s">
+      <c r="U21" s="3">
+        <v>100</v>
+      </c>
+      <c r="V21" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="U21" s="3">
-        <v>100</v>
-      </c>
-      <c r="V21" s="3" t="s">
+      <c r="W21" s="3">
+        <v>10</v>
+      </c>
+      <c r="X21" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="W21" s="3">
-        <v>10</v>
-      </c>
-      <c r="X21" s="3" t="s">
+      <c r="Y21" s="3">
+        <v>10</v>
+      </c>
+      <c r="Z21" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="Y21" s="3">
-        <v>10</v>
-      </c>
-      <c r="Z21" s="3" t="s">
-        <v>66</v>
       </c>
       <c r="AA21" s="3">
         <v>1</v>
@@ -2321,13 +2322,13 @@
         <v>63</v>
       </c>
       <c r="C22" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="F22" s="3" t="s">
         <v>107</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>108</v>
       </c>
       <c r="G22" s="3">
         <v>21</v>
@@ -2336,52 +2337,52 @@
         <v>6.6</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L22" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="M22" s="3">
+        <v>10</v>
+      </c>
+      <c r="N22" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="M22" s="3">
-        <v>10</v>
-      </c>
-      <c r="N22" s="3" t="s">
+      <c r="O22" s="3">
+        <v>10</v>
+      </c>
+      <c r="P22" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="O22" s="3">
-        <v>10</v>
-      </c>
-      <c r="P22" s="3" t="s">
+      <c r="Q22" s="3">
+        <v>10</v>
+      </c>
+      <c r="R22" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="Q22" s="3">
-        <v>10</v>
-      </c>
-      <c r="R22" s="3" t="s">
+      <c r="S22" s="3">
+        <v>100</v>
+      </c>
+      <c r="T22" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="S22" s="3">
-        <v>100</v>
-      </c>
-      <c r="T22" s="3" t="s">
+      <c r="U22" s="3">
+        <v>100</v>
+      </c>
+      <c r="V22" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="U22" s="3">
-        <v>100</v>
-      </c>
-      <c r="V22" s="3" t="s">
+      <c r="W22" s="3">
+        <v>10</v>
+      </c>
+      <c r="X22" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="W22" s="3">
-        <v>10</v>
-      </c>
-      <c r="X22" s="3" t="s">
+      <c r="Y22" s="3">
+        <v>10</v>
+      </c>
+      <c r="Z22" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>10</v>
-      </c>
-      <c r="Z22" s="3" t="s">
-        <v>66</v>
       </c>
       <c r="AA22" s="3">
         <v>1</v>
@@ -2392,13 +2393,13 @@
         <v>64</v>
       </c>
       <c r="C23" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="F23" s="3" t="s">
         <v>109</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>110</v>
       </c>
       <c r="G23" s="3">
         <v>21</v>
@@ -2407,52 +2408,52 @@
         <v>7.7</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L23" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="M23" s="3">
+        <v>10</v>
+      </c>
+      <c r="N23" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="M23" s="3">
-        <v>10</v>
-      </c>
-      <c r="N23" s="3" t="s">
+      <c r="O23" s="3">
+        <v>10</v>
+      </c>
+      <c r="P23" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="O23" s="3">
-        <v>10</v>
-      </c>
-      <c r="P23" s="3" t="s">
+      <c r="Q23" s="3">
+        <v>10</v>
+      </c>
+      <c r="R23" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="Q23" s="3">
-        <v>10</v>
-      </c>
-      <c r="R23" s="3" t="s">
+      <c r="S23" s="3">
+        <v>100</v>
+      </c>
+      <c r="T23" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="S23" s="3">
-        <v>100</v>
-      </c>
-      <c r="T23" s="3" t="s">
+      <c r="U23" s="3">
+        <v>100</v>
+      </c>
+      <c r="V23" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="U23" s="3">
-        <v>100</v>
-      </c>
-      <c r="V23" s="3" t="s">
+      <c r="W23" s="3">
+        <v>10</v>
+      </c>
+      <c r="X23" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="W23" s="3">
-        <v>10</v>
-      </c>
-      <c r="X23" s="3" t="s">
+      <c r="Y23" s="3">
+        <v>10</v>
+      </c>
+      <c r="Z23" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="Y23" s="3">
-        <v>10</v>
-      </c>
-      <c r="Z23" s="3" t="s">
-        <v>66</v>
       </c>
       <c r="AA23" s="3">
         <v>1</v>
@@ -2463,13 +2464,13 @@
         <v>65</v>
       </c>
       <c r="C24" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="F24" s="3" t="s">
         <v>111</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>112</v>
       </c>
       <c r="G24" s="3">
         <v>301</v>
@@ -2478,52 +2479,52 @@
         <v>5.5</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L24" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="M24" s="3">
+        <v>10</v>
+      </c>
+      <c r="N24" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="M24" s="3">
-        <v>10</v>
-      </c>
-      <c r="N24" s="3" t="s">
+      <c r="O24" s="3">
+        <v>10</v>
+      </c>
+      <c r="P24" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="O24" s="3">
-        <v>10</v>
-      </c>
-      <c r="P24" s="3" t="s">
+      <c r="Q24" s="3">
+        <v>10</v>
+      </c>
+      <c r="R24" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="Q24" s="3">
-        <v>10</v>
-      </c>
-      <c r="R24" s="3" t="s">
+      <c r="S24" s="3">
+        <v>100</v>
+      </c>
+      <c r="T24" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="S24" s="3">
-        <v>100</v>
-      </c>
-      <c r="T24" s="3" t="s">
+      <c r="U24" s="3">
+        <v>100</v>
+      </c>
+      <c r="V24" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="U24" s="3">
-        <v>100</v>
-      </c>
-      <c r="V24" s="3" t="s">
+      <c r="W24" s="3">
+        <v>10</v>
+      </c>
+      <c r="X24" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="W24" s="3">
-        <v>10</v>
-      </c>
-      <c r="X24" s="3" t="s">
+      <c r="Y24" s="3">
+        <v>10</v>
+      </c>
+      <c r="Z24" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="Y24" s="3">
-        <v>10</v>
-      </c>
-      <c r="Z24" s="3" t="s">
-        <v>66</v>
       </c>
       <c r="AA24" s="3">
         <v>1</v>
@@ -2534,13 +2535,13 @@
         <v>66</v>
       </c>
       <c r="C25" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D25" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="F25" s="3" t="s">
         <v>114</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>115</v>
       </c>
       <c r="G25" s="3">
         <v>21</v>
@@ -2549,52 +2550,52 @@
         <v>6.6</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L25" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="M25" s="3">
+        <v>10</v>
+      </c>
+      <c r="N25" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="M25" s="3">
-        <v>10</v>
-      </c>
-      <c r="N25" s="3" t="s">
+      <c r="O25" s="3">
+        <v>10</v>
+      </c>
+      <c r="P25" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="O25" s="3">
-        <v>10</v>
-      </c>
-      <c r="P25" s="3" t="s">
+      <c r="Q25" s="3">
+        <v>10</v>
+      </c>
+      <c r="R25" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="Q25" s="3">
-        <v>10</v>
-      </c>
-      <c r="R25" s="3" t="s">
+      <c r="S25" s="3">
+        <v>100</v>
+      </c>
+      <c r="T25" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="S25" s="3">
-        <v>100</v>
-      </c>
-      <c r="T25" s="3" t="s">
+      <c r="U25" s="3">
+        <v>100</v>
+      </c>
+      <c r="V25" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="U25" s="3">
-        <v>100</v>
-      </c>
-      <c r="V25" s="3" t="s">
+      <c r="W25" s="3">
+        <v>10</v>
+      </c>
+      <c r="X25" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="W25" s="3">
-        <v>10</v>
-      </c>
-      <c r="X25" s="3" t="s">
+      <c r="Y25" s="3">
+        <v>10</v>
+      </c>
+      <c r="Z25" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="Y25" s="3">
-        <v>10</v>
-      </c>
-      <c r="Z25" s="3" t="s">
-        <v>66</v>
       </c>
       <c r="AA25" s="3">
         <v>1</v>
@@ -2605,13 +2606,13 @@
         <v>67</v>
       </c>
       <c r="C26" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="F26" s="3" t="s">
         <v>117</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>118</v>
       </c>
       <c r="G26" s="3">
         <v>21</v>
@@ -2620,52 +2621,52 @@
         <v>7.7</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L26" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="M26" s="3">
+        <v>10</v>
+      </c>
+      <c r="N26" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="M26" s="3">
-        <v>10</v>
-      </c>
-      <c r="N26" s="3" t="s">
+      <c r="O26" s="3">
+        <v>10</v>
+      </c>
+      <c r="P26" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="O26" s="3">
-        <v>10</v>
-      </c>
-      <c r="P26" s="3" t="s">
+      <c r="Q26" s="3">
+        <v>10</v>
+      </c>
+      <c r="R26" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="Q26" s="3">
-        <v>10</v>
-      </c>
-      <c r="R26" s="3" t="s">
+      <c r="S26" s="3">
+        <v>100</v>
+      </c>
+      <c r="T26" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="S26" s="3">
-        <v>100</v>
-      </c>
-      <c r="T26" s="3" t="s">
+      <c r="U26" s="3">
+        <v>100</v>
+      </c>
+      <c r="V26" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="U26" s="3">
-        <v>100</v>
-      </c>
-      <c r="V26" s="3" t="s">
+      <c r="W26" s="3">
+        <v>10</v>
+      </c>
+      <c r="X26" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="W26" s="3">
-        <v>10</v>
-      </c>
-      <c r="X26" s="3" t="s">
+      <c r="Y26" s="3">
+        <v>10</v>
+      </c>
+      <c r="Z26" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="Y26" s="3">
-        <v>10</v>
-      </c>
-      <c r="Z26" s="3" t="s">
-        <v>66</v>
       </c>
       <c r="AA26" s="3">
         <v>1</v>

--- a/Development/Common/GameData/Monster.xlsx
+++ b/Development/Common/GameData/Monster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\MMOGameServerProject\Development\Common\GameData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B7C2637-BAF7-435B-948D-2966D81C4C96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3902650-31BD-4993-8C16-37E9B532CBE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3495" yWindow="3585" windowWidth="31605" windowHeight="17295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Monster" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="125">
   <si>
     <t>데이터이름</t>
   </si>
@@ -456,6 +456,30 @@
   </si>
   <si>
     <t>int32</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillKey1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillKey2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>몬스터 스킬</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillKey1 에는 반드시 값이 있어야 함</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>몬스터AI</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>AIKey</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -919,7 +943,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AA26"/>
+  <dimension ref="A1:AD26"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.25" style="12" customWidth="1"/>
@@ -932,16 +956,16 @@
     <col min="8" max="8" width="13.375" style="3" customWidth="1"/>
     <col min="9" max="9" width="17.5" style="3" customWidth="1"/>
     <col min="10" max="10" width="16.75" style="3" customWidth="1"/>
-    <col min="11" max="11" width="20.875" style="3" customWidth="1"/>
-    <col min="12" max="13" width="15.625" style="3" customWidth="1"/>
-    <col min="14" max="14" width="13.25" style="3" customWidth="1"/>
-    <col min="15" max="15" width="16.375" style="3" customWidth="1"/>
-    <col min="16" max="16" width="15.625" style="3" customWidth="1"/>
-    <col min="17" max="17" width="16.25" style="3" customWidth="1"/>
-    <col min="18" max="16384" width="9" style="3"/>
+    <col min="11" max="14" width="20.875" style="3" customWidth="1"/>
+    <col min="15" max="16" width="15.625" style="3" customWidth="1"/>
+    <col min="17" max="17" width="13.25" style="3" customWidth="1"/>
+    <col min="18" max="18" width="16.375" style="3" customWidth="1"/>
+    <col min="19" max="19" width="15.625" style="3" customWidth="1"/>
+    <col min="20" max="20" width="16.25" style="3" customWidth="1"/>
+    <col min="21" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -949,7 +973,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -980,11 +1004,15 @@
         <v>36</v>
       </c>
       <c r="L2" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
       <c r="P2" s="4"/>
       <c r="Q2" s="4"/>
       <c r="R2" s="4"/>
@@ -997,8 +1025,11 @@
       <c r="Y2" s="4"/>
       <c r="Z2" s="4"/>
       <c r="AA2" s="4"/>
+      <c r="AB2" s="4"/>
+      <c r="AC2" s="4"/>
+      <c r="AD2" s="4"/>
     </row>
-    <row r="3" spans="1:27" s="7" customFormat="1" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:30" s="7" customFormat="1" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
@@ -1025,7 +1056,9 @@
       </c>
       <c r="K3" s="6"/>
       <c r="L3" s="6"/>
-      <c r="M3" s="6"/>
+      <c r="M3" s="6" t="s">
+        <v>122</v>
+      </c>
       <c r="N3" s="6"/>
       <c r="O3" s="6"/>
       <c r="P3" s="6"/>
@@ -1040,8 +1073,11 @@
       <c r="Y3" s="6"/>
       <c r="Z3" s="6"/>
       <c r="AA3" s="6"/>
+      <c r="AB3" s="6"/>
+      <c r="AC3" s="6"/>
+      <c r="AD3" s="6"/>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -1076,7 +1112,7 @@
         <v>20</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M4" s="8" t="s">
         <v>20</v>
@@ -1123,8 +1159,17 @@
       <c r="AA4" s="8" t="s">
         <v>20</v>
       </c>
+      <c r="AB4" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="AC4" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="AD4" s="8" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
@@ -1155,55 +1200,64 @@
         <v>33</v>
       </c>
       <c r="L5" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="M5" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="N5" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="O5" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="M5" s="8" t="s">
+      <c r="P5" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="N5" s="8" t="s">
+      <c r="Q5" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="O5" s="8" t="s">
+      <c r="R5" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="P5" s="8" t="s">
+      <c r="S5" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="Q5" s="8" t="s">
+      <c r="T5" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="R5" s="8" t="s">
+      <c r="U5" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="S5" s="8" t="s">
+      <c r="V5" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="T5" s="8" t="s">
+      <c r="W5" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="U5" s="8" t="s">
+      <c r="X5" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="V5" s="8" t="s">
+      <c r="Y5" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="W5" s="8" t="s">
+      <c r="Z5" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="X5" s="8" t="s">
+      <c r="AA5" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="Y5" s="8" t="s">
+      <c r="AB5" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="Z5" s="8" t="s">
+      <c r="AC5" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="AA5" s="8" t="s">
+      <c r="AD5" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -1219,40 +1273,43 @@
       <c r="K6" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L6" s="8" t="s">
+      <c r="L6" s="8"/>
+      <c r="M6" s="8"/>
+      <c r="N6" s="8"/>
+      <c r="O6" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="M6" s="8"/>
-      <c r="N6" s="8" t="s">
+      <c r="P6" s="8"/>
+      <c r="Q6" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="O6" s="8"/>
-      <c r="P6" s="8" t="s">
+      <c r="R6" s="8"/>
+      <c r="S6" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="Q6" s="8"/>
-      <c r="R6" s="8" t="s">
+      <c r="T6" s="8"/>
+      <c r="U6" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="S6" s="8"/>
-      <c r="T6" s="8" t="s">
+      <c r="V6" s="8"/>
+      <c r="W6" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="U6" s="8"/>
-      <c r="V6" s="8" t="s">
+      <c r="X6" s="8"/>
+      <c r="Y6" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="W6" s="8"/>
-      <c r="X6" s="8" t="s">
+      <c r="Z6" s="8"/>
+      <c r="AA6" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="Y6" s="8"/>
-      <c r="Z6" s="8" t="s">
+      <c r="AB6" s="8"/>
+      <c r="AC6" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="AA6" s="8"/>
+      <c r="AD6" s="8"/>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
@@ -1278,40 +1335,49 @@
       <c r="K7" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="L7" s="8"/>
+      <c r="L7" s="8">
+        <v>0</v>
+      </c>
       <c r="M7" s="8">
         <v>0</v>
       </c>
-      <c r="N7" s="8"/>
-      <c r="O7" s="8">
+      <c r="N7" s="8">
         <v>0</v>
       </c>
-      <c r="P7" s="8"/>
-      <c r="Q7" s="8">
+      <c r="O7" s="8"/>
+      <c r="P7" s="8">
         <v>0</v>
       </c>
-      <c r="R7" s="8"/>
-      <c r="S7" s="8">
+      <c r="Q7" s="8"/>
+      <c r="R7" s="8">
         <v>0</v>
       </c>
-      <c r="T7" s="8"/>
-      <c r="U7" s="8">
+      <c r="S7" s="8"/>
+      <c r="T7" s="8">
         <v>0</v>
       </c>
-      <c r="V7" s="8"/>
-      <c r="W7" s="8">
+      <c r="U7" s="8"/>
+      <c r="V7" s="8">
         <v>0</v>
       </c>
-      <c r="X7" s="8"/>
-      <c r="Y7" s="8">
+      <c r="W7" s="8"/>
+      <c r="X7" s="8">
         <v>0</v>
       </c>
-      <c r="Z7" s="8"/>
-      <c r="AA7" s="8">
+      <c r="Y7" s="8"/>
+      <c r="Z7" s="8">
         <v>0</v>
       </c>
+      <c r="AA7" s="8"/>
+      <c r="AB7" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="8"/>
+      <c r="AD7" s="8">
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="1:27" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:30" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>12</v>
       </c>
@@ -1346,55 +1412,64 @@
         <v>35</v>
       </c>
       <c r="L8" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="M8" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="N8" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="O8" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="M8" s="10" t="s">
+      <c r="P8" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="N8" s="10" t="s">
+      <c r="Q8" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="O8" s="10" t="s">
+      <c r="R8" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="P8" s="10" t="s">
+      <c r="S8" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="Q8" s="10" t="s">
+      <c r="T8" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="R8" s="10" t="s">
+      <c r="U8" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="S8" s="10" t="s">
+      <c r="V8" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="T8" s="10" t="s">
+      <c r="W8" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="U8" s="10" t="s">
+      <c r="X8" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="V8" s="10" t="s">
+      <c r="Y8" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="W8" s="10" t="s">
+      <c r="Z8" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="X8" s="10" t="s">
+      <c r="AA8" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="Y8" s="10" t="s">
+      <c r="AB8" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="Z8" s="10" t="s">
+      <c r="AC8" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="AA8" s="10" t="s">
+      <c r="AD8" s="10" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B9" s="3">
         <v>50</v>
       </c>
@@ -1416,56 +1491,62 @@
       <c r="K9" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="L9" s="3" t="s">
+      <c r="L9" s="3">
+        <v>1002</v>
+      </c>
+      <c r="M9" s="3">
+        <v>9002</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="P9" s="3">
+        <v>5</v>
+      </c>
+      <c r="Q9" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="M9" s="3">
-        <v>10</v>
-      </c>
-      <c r="N9" s="3" t="s">
+      <c r="R9" s="3">
+        <v>10</v>
+      </c>
+      <c r="S9" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="O9" s="3">
-        <v>10</v>
-      </c>
-      <c r="P9" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q9" s="3">
-        <v>10</v>
-      </c>
-      <c r="R9" s="3" t="s">
+      <c r="T9" s="3">
+        <v>10</v>
+      </c>
+      <c r="U9" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="S9" s="3">
+      <c r="V9" s="3">
+        <v>1000</v>
+      </c>
+      <c r="W9" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="X9" s="3">
         <v>100</v>
       </c>
-      <c r="T9" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="U9" s="3">
-        <v>100</v>
-      </c>
-      <c r="V9" s="3" t="s">
+      <c r="Y9" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="W9" s="3">
-        <v>10</v>
-      </c>
-      <c r="X9" s="3" t="s">
+      <c r="Z9" s="3">
+        <v>10</v>
+      </c>
+      <c r="AA9" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="Y9" s="3">
-        <v>10</v>
-      </c>
-      <c r="Z9" s="3" t="s">
+      <c r="AB9" s="3">
+        <v>10</v>
+      </c>
+      <c r="AC9" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AD9" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B10" s="3">
         <v>51</v>
       </c>
@@ -1487,56 +1568,62 @@
       <c r="K10" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="L10" s="3" t="s">
+      <c r="L10" s="3">
+        <v>1001</v>
+      </c>
+      <c r="M10" s="3">
+        <v>9001</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="P10" s="3">
+        <v>5</v>
+      </c>
+      <c r="Q10" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="M10" s="3">
-        <v>10</v>
-      </c>
-      <c r="N10" s="3" t="s">
+      <c r="R10" s="3">
+        <v>10</v>
+      </c>
+      <c r="S10" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="O10" s="3">
-        <v>10</v>
-      </c>
-      <c r="P10" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q10" s="3">
-        <v>10</v>
-      </c>
-      <c r="R10" s="3" t="s">
+      <c r="T10" s="3">
+        <v>10</v>
+      </c>
+      <c r="U10" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="S10" s="3">
+      <c r="V10" s="3">
+        <v>1000</v>
+      </c>
+      <c r="W10" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="X10" s="3">
         <v>100</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="U10" s="3">
-        <v>100</v>
-      </c>
-      <c r="V10" s="3" t="s">
+      <c r="Y10" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="W10" s="3">
-        <v>10</v>
-      </c>
-      <c r="X10" s="3" t="s">
+      <c r="Z10" s="3">
+        <v>10</v>
+      </c>
+      <c r="AA10" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="Y10" s="3">
-        <v>10</v>
-      </c>
-      <c r="Z10" s="3" t="s">
+      <c r="AB10" s="3">
+        <v>10</v>
+      </c>
+      <c r="AC10" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AD10" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B11" s="3">
         <v>52</v>
       </c>
@@ -1558,56 +1645,62 @@
       <c r="K11" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="L11" s="3" t="s">
+      <c r="L11" s="3">
+        <v>1001</v>
+      </c>
+      <c r="M11" s="3">
+        <v>9001</v>
+      </c>
+      <c r="O11" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="P11" s="3">
+        <v>5</v>
+      </c>
+      <c r="Q11" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="M11" s="3">
-        <v>10</v>
-      </c>
-      <c r="N11" s="3" t="s">
+      <c r="R11" s="3">
+        <v>10</v>
+      </c>
+      <c r="S11" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="O11" s="3">
-        <v>10</v>
-      </c>
-      <c r="P11" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q11" s="3">
-        <v>10</v>
-      </c>
-      <c r="R11" s="3" t="s">
+      <c r="T11" s="3">
+        <v>10</v>
+      </c>
+      <c r="U11" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="S11" s="3">
+      <c r="V11" s="3">
+        <v>1000</v>
+      </c>
+      <c r="W11" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="X11" s="3">
         <v>100</v>
       </c>
-      <c r="T11" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="U11" s="3">
-        <v>100</v>
-      </c>
-      <c r="V11" s="3" t="s">
+      <c r="Y11" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="W11" s="3">
-        <v>10</v>
-      </c>
-      <c r="X11" s="3" t="s">
+      <c r="Z11" s="3">
+        <v>10</v>
+      </c>
+      <c r="AA11" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="Y11" s="3">
-        <v>10</v>
-      </c>
-      <c r="Z11" s="3" t="s">
+      <c r="AB11" s="3">
+        <v>10</v>
+      </c>
+      <c r="AC11" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="AA11" s="3">
+      <c r="AD11" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B12" s="3">
         <v>53</v>
       </c>
@@ -1629,56 +1722,62 @@
       <c r="K12" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="L12" s="3" t="s">
+      <c r="L12" s="3">
+        <v>1001</v>
+      </c>
+      <c r="M12" s="3">
+        <v>9001</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="P12" s="3">
+        <v>5</v>
+      </c>
+      <c r="Q12" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="M12" s="3">
-        <v>10</v>
-      </c>
-      <c r="N12" s="3" t="s">
+      <c r="R12" s="3">
+        <v>10</v>
+      </c>
+      <c r="S12" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="O12" s="3">
-        <v>10</v>
-      </c>
-      <c r="P12" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>10</v>
-      </c>
-      <c r="R12" s="3" t="s">
+      <c r="T12" s="3">
+        <v>10</v>
+      </c>
+      <c r="U12" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="S12" s="3">
+      <c r="V12" s="3">
+        <v>1000</v>
+      </c>
+      <c r="W12" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="X12" s="3">
         <v>100</v>
       </c>
-      <c r="T12" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="U12" s="3">
-        <v>100</v>
-      </c>
-      <c r="V12" s="3" t="s">
+      <c r="Y12" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="W12" s="3">
-        <v>10</v>
-      </c>
-      <c r="X12" s="3" t="s">
+      <c r="Z12" s="3">
+        <v>10</v>
+      </c>
+      <c r="AA12" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="Y12" s="3">
-        <v>10</v>
-      </c>
-      <c r="Z12" s="3" t="s">
+      <c r="AB12" s="3">
+        <v>10</v>
+      </c>
+      <c r="AC12" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AD12" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B13" s="3">
         <v>54</v>
       </c>
@@ -1700,56 +1799,62 @@
       <c r="K13" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="L13" s="3" t="s">
+      <c r="L13" s="3">
+        <v>1001</v>
+      </c>
+      <c r="M13" s="3">
+        <v>9001</v>
+      </c>
+      <c r="O13" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="P13" s="3">
+        <v>5</v>
+      </c>
+      <c r="Q13" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="M13" s="3">
-        <v>10</v>
-      </c>
-      <c r="N13" s="3" t="s">
+      <c r="R13" s="3">
+        <v>10</v>
+      </c>
+      <c r="S13" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="O13" s="3">
-        <v>10</v>
-      </c>
-      <c r="P13" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q13" s="3">
-        <v>10</v>
-      </c>
-      <c r="R13" s="3" t="s">
+      <c r="T13" s="3">
+        <v>10</v>
+      </c>
+      <c r="U13" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="S13" s="3">
+      <c r="V13" s="3">
+        <v>1000</v>
+      </c>
+      <c r="W13" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="X13" s="3">
         <v>100</v>
       </c>
-      <c r="T13" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="U13" s="3">
-        <v>100</v>
-      </c>
-      <c r="V13" s="3" t="s">
+      <c r="Y13" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="W13" s="3">
-        <v>10</v>
-      </c>
-      <c r="X13" s="3" t="s">
+      <c r="Z13" s="3">
+        <v>10</v>
+      </c>
+      <c r="AA13" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="Y13" s="3">
-        <v>10</v>
-      </c>
-      <c r="Z13" s="3" t="s">
+      <c r="AB13" s="3">
+        <v>10</v>
+      </c>
+      <c r="AC13" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="AA13" s="3">
+      <c r="AD13" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B14" s="3">
         <v>55</v>
       </c>
@@ -1771,56 +1876,62 @@
       <c r="K14" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="L14" s="3" t="s">
+      <c r="L14" s="3">
+        <v>1002</v>
+      </c>
+      <c r="M14" s="3">
+        <v>9002</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="P14" s="3">
+        <v>5</v>
+      </c>
+      <c r="Q14" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="M14" s="3">
-        <v>10</v>
-      </c>
-      <c r="N14" s="3" t="s">
+      <c r="R14" s="3">
+        <v>10</v>
+      </c>
+      <c r="S14" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="O14" s="3">
-        <v>10</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>10</v>
-      </c>
-      <c r="R14" s="3" t="s">
+      <c r="T14" s="3">
+        <v>10</v>
+      </c>
+      <c r="U14" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="S14" s="3">
+      <c r="V14" s="3">
+        <v>1000</v>
+      </c>
+      <c r="W14" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="X14" s="3">
         <v>100</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="U14" s="3">
-        <v>100</v>
-      </c>
-      <c r="V14" s="3" t="s">
+      <c r="Y14" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="W14" s="3">
-        <v>10</v>
-      </c>
-      <c r="X14" s="3" t="s">
+      <c r="Z14" s="3">
+        <v>10</v>
+      </c>
+      <c r="AA14" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="Y14" s="3">
-        <v>10</v>
-      </c>
-      <c r="Z14" s="3" t="s">
+      <c r="AB14" s="3">
+        <v>10</v>
+      </c>
+      <c r="AC14" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AD14" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B15" s="3">
         <v>56</v>
       </c>
@@ -1842,56 +1953,62 @@
       <c r="K15" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="L15" s="3" t="s">
+      <c r="L15" s="3">
+        <v>1002</v>
+      </c>
+      <c r="M15" s="3">
+        <v>9002</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="P15" s="3">
+        <v>5</v>
+      </c>
+      <c r="Q15" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="M15" s="3">
-        <v>10</v>
-      </c>
-      <c r="N15" s="3" t="s">
+      <c r="R15" s="3">
+        <v>10</v>
+      </c>
+      <c r="S15" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="O15" s="3">
-        <v>10</v>
-      </c>
-      <c r="P15" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>10</v>
-      </c>
-      <c r="R15" s="3" t="s">
+      <c r="T15" s="3">
+        <v>10</v>
+      </c>
+      <c r="U15" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="S15" s="3">
+      <c r="V15" s="3">
+        <v>1000</v>
+      </c>
+      <c r="W15" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="X15" s="3">
         <v>100</v>
       </c>
-      <c r="T15" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="U15" s="3">
-        <v>100</v>
-      </c>
-      <c r="V15" s="3" t="s">
+      <c r="Y15" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="W15" s="3">
-        <v>10</v>
-      </c>
-      <c r="X15" s="3" t="s">
+      <c r="Z15" s="3">
+        <v>10</v>
+      </c>
+      <c r="AA15" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="Y15" s="3">
-        <v>10</v>
-      </c>
-      <c r="Z15" s="3" t="s">
+      <c r="AB15" s="3">
+        <v>10</v>
+      </c>
+      <c r="AC15" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AD15" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B16" s="3">
         <v>57</v>
       </c>
@@ -1913,56 +2030,62 @@
       <c r="K16" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="L16" s="3" t="s">
+      <c r="L16" s="3">
+        <v>1002</v>
+      </c>
+      <c r="M16" s="3">
+        <v>9002</v>
+      </c>
+      <c r="O16" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="P16" s="3">
+        <v>5</v>
+      </c>
+      <c r="Q16" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="M16" s="3">
-        <v>10</v>
-      </c>
-      <c r="N16" s="3" t="s">
+      <c r="R16" s="3">
+        <v>10</v>
+      </c>
+      <c r="S16" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="O16" s="3">
-        <v>10</v>
-      </c>
-      <c r="P16" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q16" s="3">
-        <v>10</v>
-      </c>
-      <c r="R16" s="3" t="s">
+      <c r="T16" s="3">
+        <v>10</v>
+      </c>
+      <c r="U16" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="S16" s="3">
+      <c r="V16" s="3">
+        <v>1000</v>
+      </c>
+      <c r="W16" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="X16" s="3">
         <v>100</v>
       </c>
-      <c r="T16" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="U16" s="3">
-        <v>100</v>
-      </c>
-      <c r="V16" s="3" t="s">
+      <c r="Y16" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="W16" s="3">
-        <v>10</v>
-      </c>
-      <c r="X16" s="3" t="s">
+      <c r="Z16" s="3">
+        <v>10</v>
+      </c>
+      <c r="AA16" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="Y16" s="3">
-        <v>10</v>
-      </c>
-      <c r="Z16" s="3" t="s">
+      <c r="AB16" s="3">
+        <v>10</v>
+      </c>
+      <c r="AC16" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="AA16" s="3">
+      <c r="AD16" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B17" s="3">
         <v>58</v>
       </c>
@@ -1984,56 +2107,62 @@
       <c r="K17" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="L17" s="3" t="s">
+      <c r="L17" s="3">
+        <v>1002</v>
+      </c>
+      <c r="M17" s="3">
+        <v>9002</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="P17" s="3">
+        <v>5</v>
+      </c>
+      <c r="Q17" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="M17" s="3">
-        <v>10</v>
-      </c>
-      <c r="N17" s="3" t="s">
+      <c r="R17" s="3">
+        <v>10</v>
+      </c>
+      <c r="S17" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="O17" s="3">
-        <v>10</v>
-      </c>
-      <c r="P17" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q17" s="3">
-        <v>10</v>
-      </c>
-      <c r="R17" s="3" t="s">
+      <c r="T17" s="3">
+        <v>10</v>
+      </c>
+      <c r="U17" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="S17" s="3">
+      <c r="V17" s="3">
+        <v>1000</v>
+      </c>
+      <c r="W17" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="X17" s="3">
         <v>100</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="U17" s="3">
-        <v>100</v>
-      </c>
-      <c r="V17" s="3" t="s">
+      <c r="Y17" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="W17" s="3">
-        <v>10</v>
-      </c>
-      <c r="X17" s="3" t="s">
+      <c r="Z17" s="3">
+        <v>10</v>
+      </c>
+      <c r="AA17" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="Y17" s="3">
-        <v>10</v>
-      </c>
-      <c r="Z17" s="3" t="s">
+      <c r="AB17" s="3">
+        <v>10</v>
+      </c>
+      <c r="AC17" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AD17" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B18" s="3">
         <v>59</v>
       </c>
@@ -2055,56 +2184,62 @@
       <c r="K18" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="L18" s="3" t="s">
+      <c r="L18" s="3">
+        <v>1002</v>
+      </c>
+      <c r="M18" s="3">
+        <v>9002</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="P18" s="3">
+        <v>5</v>
+      </c>
+      <c r="Q18" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="M18" s="3">
-        <v>10</v>
-      </c>
-      <c r="N18" s="3" t="s">
+      <c r="R18" s="3">
+        <v>10</v>
+      </c>
+      <c r="S18" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="O18" s="3">
-        <v>10</v>
-      </c>
-      <c r="P18" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>10</v>
-      </c>
-      <c r="R18" s="3" t="s">
+      <c r="T18" s="3">
+        <v>10</v>
+      </c>
+      <c r="U18" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="S18" s="3">
+      <c r="V18" s="3">
+        <v>1000</v>
+      </c>
+      <c r="W18" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="X18" s="3">
         <v>100</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="U18" s="3">
-        <v>100</v>
-      </c>
-      <c r="V18" s="3" t="s">
+      <c r="Y18" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="W18" s="3">
-        <v>10</v>
-      </c>
-      <c r="X18" s="3" t="s">
+      <c r="Z18" s="3">
+        <v>10</v>
+      </c>
+      <c r="AA18" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="Y18" s="3">
-        <v>10</v>
-      </c>
-      <c r="Z18" s="3" t="s">
+      <c r="AB18" s="3">
+        <v>10</v>
+      </c>
+      <c r="AC18" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AD18" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B19" s="3">
         <v>60</v>
       </c>
@@ -2126,56 +2261,62 @@
       <c r="K19" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="L19" s="3" t="s">
+      <c r="L19" s="3">
+        <v>1002</v>
+      </c>
+      <c r="M19" s="3">
+        <v>9002</v>
+      </c>
+      <c r="O19" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="P19" s="3">
+        <v>5</v>
+      </c>
+      <c r="Q19" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="M19" s="3">
-        <v>10</v>
-      </c>
-      <c r="N19" s="3" t="s">
+      <c r="R19" s="3">
+        <v>10</v>
+      </c>
+      <c r="S19" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="O19" s="3">
-        <v>10</v>
-      </c>
-      <c r="P19" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q19" s="3">
-        <v>10</v>
-      </c>
-      <c r="R19" s="3" t="s">
+      <c r="T19" s="3">
+        <v>10</v>
+      </c>
+      <c r="U19" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="S19" s="3">
+      <c r="V19" s="3">
+        <v>1000</v>
+      </c>
+      <c r="W19" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="X19" s="3">
         <v>100</v>
       </c>
-      <c r="T19" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="U19" s="3">
-        <v>100</v>
-      </c>
-      <c r="V19" s="3" t="s">
+      <c r="Y19" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="W19" s="3">
-        <v>10</v>
-      </c>
-      <c r="X19" s="3" t="s">
+      <c r="Z19" s="3">
+        <v>10</v>
+      </c>
+      <c r="AA19" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="Y19" s="3">
-        <v>10</v>
-      </c>
-      <c r="Z19" s="3" t="s">
+      <c r="AB19" s="3">
+        <v>10</v>
+      </c>
+      <c r="AC19" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="AA19" s="3">
+      <c r="AD19" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B20" s="3">
         <v>61</v>
       </c>
@@ -2197,56 +2338,65 @@
       <c r="K20" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="L20" s="3" t="s">
+      <c r="L20" s="3">
+        <v>1002</v>
+      </c>
+      <c r="M20" s="3">
+        <v>9002</v>
+      </c>
+      <c r="N20" s="3">
+        <v>9001</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="P20" s="3">
+        <v>5</v>
+      </c>
+      <c r="Q20" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="M20" s="3">
-        <v>10</v>
-      </c>
-      <c r="N20" s="3" t="s">
+      <c r="R20" s="3">
+        <v>10</v>
+      </c>
+      <c r="S20" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="O20" s="3">
-        <v>10</v>
-      </c>
-      <c r="P20" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>10</v>
-      </c>
-      <c r="R20" s="3" t="s">
+      <c r="T20" s="3">
+        <v>10</v>
+      </c>
+      <c r="U20" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="S20" s="3">
+      <c r="V20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="W20" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="X20" s="3">
         <v>100</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="U20" s="3">
-        <v>100</v>
-      </c>
-      <c r="V20" s="3" t="s">
+      <c r="Y20" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="W20" s="3">
-        <v>10</v>
-      </c>
-      <c r="X20" s="3" t="s">
+      <c r="Z20" s="3">
+        <v>10</v>
+      </c>
+      <c r="AA20" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="Y20" s="3">
-        <v>10</v>
-      </c>
-      <c r="Z20" s="3" t="s">
+      <c r="AB20" s="3">
+        <v>10</v>
+      </c>
+      <c r="AC20" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AD20" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B21" s="3">
         <v>62</v>
       </c>
@@ -2268,56 +2418,65 @@
       <c r="K21" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="L21" s="3" t="s">
+      <c r="L21" s="3">
+        <v>1002</v>
+      </c>
+      <c r="M21" s="3">
+        <v>9002</v>
+      </c>
+      <c r="N21" s="3">
+        <v>9001</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="P21" s="3">
+        <v>5</v>
+      </c>
+      <c r="Q21" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="M21" s="3">
-        <v>10</v>
-      </c>
-      <c r="N21" s="3" t="s">
+      <c r="R21" s="3">
+        <v>10</v>
+      </c>
+      <c r="S21" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="O21" s="3">
-        <v>10</v>
-      </c>
-      <c r="P21" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q21" s="3">
-        <v>10</v>
-      </c>
-      <c r="R21" s="3" t="s">
+      <c r="T21" s="3">
+        <v>10</v>
+      </c>
+      <c r="U21" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="S21" s="3">
+      <c r="V21" s="3">
+        <v>1000</v>
+      </c>
+      <c r="W21" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="X21" s="3">
         <v>100</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="U21" s="3">
-        <v>100</v>
-      </c>
-      <c r="V21" s="3" t="s">
+      <c r="Y21" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="W21" s="3">
-        <v>10</v>
-      </c>
-      <c r="X21" s="3" t="s">
+      <c r="Z21" s="3">
+        <v>10</v>
+      </c>
+      <c r="AA21" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="Y21" s="3">
-        <v>10</v>
-      </c>
-      <c r="Z21" s="3" t="s">
+      <c r="AB21" s="3">
+        <v>10</v>
+      </c>
+      <c r="AC21" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AD21" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B22" s="3">
         <v>63</v>
       </c>
@@ -2339,56 +2498,65 @@
       <c r="K22" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="L22" s="3" t="s">
+      <c r="L22" s="3">
+        <v>1002</v>
+      </c>
+      <c r="M22" s="3">
+        <v>9002</v>
+      </c>
+      <c r="N22" s="3">
+        <v>9001</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="P22" s="3">
+        <v>5</v>
+      </c>
+      <c r="Q22" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="M22" s="3">
-        <v>10</v>
-      </c>
-      <c r="N22" s="3" t="s">
+      <c r="R22" s="3">
+        <v>10</v>
+      </c>
+      <c r="S22" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="O22" s="3">
-        <v>10</v>
-      </c>
-      <c r="P22" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>10</v>
-      </c>
-      <c r="R22" s="3" t="s">
+      <c r="T22" s="3">
+        <v>10</v>
+      </c>
+      <c r="U22" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="S22" s="3">
+      <c r="V22" s="3">
+        <v>1000</v>
+      </c>
+      <c r="W22" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="X22" s="3">
         <v>100</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="U22" s="3">
-        <v>100</v>
-      </c>
-      <c r="V22" s="3" t="s">
+      <c r="Y22" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="W22" s="3">
-        <v>10</v>
-      </c>
-      <c r="X22" s="3" t="s">
+      <c r="Z22" s="3">
+        <v>10</v>
+      </c>
+      <c r="AA22" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="Y22" s="3">
-        <v>10</v>
-      </c>
-      <c r="Z22" s="3" t="s">
+      <c r="AB22" s="3">
+        <v>10</v>
+      </c>
+      <c r="AC22" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AD22" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B23" s="3">
         <v>64</v>
       </c>
@@ -2410,56 +2578,65 @@
       <c r="K23" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="L23" s="3" t="s">
+      <c r="L23" s="3">
+        <v>1002</v>
+      </c>
+      <c r="M23" s="3">
+        <v>9002</v>
+      </c>
+      <c r="N23" s="3">
+        <v>9001</v>
+      </c>
+      <c r="O23" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="P23" s="3">
+        <v>5</v>
+      </c>
+      <c r="Q23" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="M23" s="3">
-        <v>10</v>
-      </c>
-      <c r="N23" s="3" t="s">
+      <c r="R23" s="3">
+        <v>10</v>
+      </c>
+      <c r="S23" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="O23" s="3">
-        <v>10</v>
-      </c>
-      <c r="P23" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q23" s="3">
-        <v>10</v>
-      </c>
-      <c r="R23" s="3" t="s">
+      <c r="T23" s="3">
+        <v>10</v>
+      </c>
+      <c r="U23" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="S23" s="3">
+      <c r="V23" s="3">
+        <v>1000</v>
+      </c>
+      <c r="W23" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="X23" s="3">
         <v>100</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="U23" s="3">
-        <v>100</v>
-      </c>
-      <c r="V23" s="3" t="s">
+      <c r="Y23" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="W23" s="3">
-        <v>10</v>
-      </c>
-      <c r="X23" s="3" t="s">
+      <c r="Z23" s="3">
+        <v>10</v>
+      </c>
+      <c r="AA23" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="Y23" s="3">
-        <v>10</v>
-      </c>
-      <c r="Z23" s="3" t="s">
+      <c r="AB23" s="3">
+        <v>10</v>
+      </c>
+      <c r="AC23" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AD23" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B24" s="3">
         <v>65</v>
       </c>
@@ -2481,56 +2658,65 @@
       <c r="K24" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="L24" s="3" t="s">
+      <c r="L24" s="3">
+        <v>1002</v>
+      </c>
+      <c r="M24" s="3">
+        <v>9002</v>
+      </c>
+      <c r="N24" s="3">
+        <v>9001</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="P24" s="3">
+        <v>5</v>
+      </c>
+      <c r="Q24" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="M24" s="3">
-        <v>10</v>
-      </c>
-      <c r="N24" s="3" t="s">
+      <c r="R24" s="3">
+        <v>10</v>
+      </c>
+      <c r="S24" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="O24" s="3">
-        <v>10</v>
-      </c>
-      <c r="P24" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>10</v>
-      </c>
-      <c r="R24" s="3" t="s">
+      <c r="T24" s="3">
+        <v>10</v>
+      </c>
+      <c r="U24" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="S24" s="3">
+      <c r="V24" s="3">
+        <v>1000</v>
+      </c>
+      <c r="W24" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="X24" s="3">
         <v>100</v>
       </c>
-      <c r="T24" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="U24" s="3">
-        <v>100</v>
-      </c>
-      <c r="V24" s="3" t="s">
+      <c r="Y24" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="W24" s="3">
-        <v>10</v>
-      </c>
-      <c r="X24" s="3" t="s">
+      <c r="Z24" s="3">
+        <v>10</v>
+      </c>
+      <c r="AA24" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="Y24" s="3">
-        <v>10</v>
-      </c>
-      <c r="Z24" s="3" t="s">
+      <c r="AB24" s="3">
+        <v>10</v>
+      </c>
+      <c r="AC24" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AD24" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B25" s="3">
         <v>66</v>
       </c>
@@ -2552,56 +2738,65 @@
       <c r="K25" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="L25" s="3" t="s">
+      <c r="L25" s="3">
+        <v>1002</v>
+      </c>
+      <c r="M25" s="3">
+        <v>9002</v>
+      </c>
+      <c r="N25" s="3">
+        <v>9001</v>
+      </c>
+      <c r="O25" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="P25" s="3">
+        <v>5</v>
+      </c>
+      <c r="Q25" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="M25" s="3">
-        <v>10</v>
-      </c>
-      <c r="N25" s="3" t="s">
+      <c r="R25" s="3">
+        <v>10</v>
+      </c>
+      <c r="S25" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="O25" s="3">
-        <v>10</v>
-      </c>
-      <c r="P25" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q25" s="3">
-        <v>10</v>
-      </c>
-      <c r="R25" s="3" t="s">
+      <c r="T25" s="3">
+        <v>10</v>
+      </c>
+      <c r="U25" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="S25" s="3">
+      <c r="V25" s="3">
+        <v>1000</v>
+      </c>
+      <c r="W25" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="X25" s="3">
         <v>100</v>
       </c>
-      <c r="T25" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="U25" s="3">
-        <v>100</v>
-      </c>
-      <c r="V25" s="3" t="s">
+      <c r="Y25" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="W25" s="3">
-        <v>10</v>
-      </c>
-      <c r="X25" s="3" t="s">
+      <c r="Z25" s="3">
+        <v>10</v>
+      </c>
+      <c r="AA25" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="Y25" s="3">
-        <v>10</v>
-      </c>
-      <c r="Z25" s="3" t="s">
+      <c r="AB25" s="3">
+        <v>10</v>
+      </c>
+      <c r="AC25" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="AA25" s="3">
+      <c r="AD25" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="2:27" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B26" s="3">
         <v>67</v>
       </c>
@@ -2623,52 +2818,61 @@
       <c r="K26" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="L26" s="3" t="s">
+      <c r="L26" s="3">
+        <v>1002</v>
+      </c>
+      <c r="M26" s="3">
+        <v>9002</v>
+      </c>
+      <c r="N26" s="3">
+        <v>9001</v>
+      </c>
+      <c r="O26" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="P26" s="3">
+        <v>5</v>
+      </c>
+      <c r="Q26" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="M26" s="3">
-        <v>10</v>
-      </c>
-      <c r="N26" s="3" t="s">
+      <c r="R26" s="3">
+        <v>10</v>
+      </c>
+      <c r="S26" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="O26" s="3">
-        <v>10</v>
-      </c>
-      <c r="P26" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q26" s="3">
-        <v>10</v>
-      </c>
-      <c r="R26" s="3" t="s">
+      <c r="T26" s="3">
+        <v>10</v>
+      </c>
+      <c r="U26" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="S26" s="3">
+      <c r="V26" s="3">
+        <v>1000</v>
+      </c>
+      <c r="W26" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="X26" s="3">
         <v>100</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="U26" s="3">
-        <v>100</v>
-      </c>
-      <c r="V26" s="3" t="s">
+      <c r="Y26" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="W26" s="3">
-        <v>10</v>
-      </c>
-      <c r="X26" s="3" t="s">
+      <c r="Z26" s="3">
+        <v>10</v>
+      </c>
+      <c r="AA26" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="Y26" s="3">
-        <v>10</v>
-      </c>
-      <c r="Z26" s="3" t="s">
+      <c r="AB26" s="3">
+        <v>10</v>
+      </c>
+      <c r="AC26" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AD26" s="3">
         <v>1</v>
       </c>
     </row>

--- a/Development/Common/GameData/Monster.xlsx
+++ b/Development/Common/GameData/Monster.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\MMOGameServerProject\Development\Common\GameData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3902650-31BD-4993-8C16-37E9B532CBE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F0DBE50-2F2F-4099-9025-AE36D6B3979B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1645,9 +1645,6 @@
       <c r="K11" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="L11" s="3">
-        <v>1001</v>
-      </c>
       <c r="M11" s="3">
         <v>9001</v>
       </c>
@@ -2262,10 +2259,10 @@
         <v>37</v>
       </c>
       <c r="L19" s="3">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="M19" s="3">
-        <v>9002</v>
+        <v>9001</v>
       </c>
       <c r="O19" s="3" t="s">
         <v>60</v>
@@ -2659,12 +2656,9 @@
         <v>37</v>
       </c>
       <c r="L24" s="3">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="M24" s="3">
-        <v>9002</v>
-      </c>
-      <c r="N24" s="3">
         <v>9001</v>
       </c>
       <c r="O24" s="3" t="s">

--- a/Development/Common/GameData/Monster.xlsx
+++ b/Development/Common/GameData/Monster.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\MMOGameServerProject\Development\Common\GameData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project\MMOGameServerProject\Development\Common\GameData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F0DBE50-2F2F-4099-9025-AE36D6B3979B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{637ADC47-D4BA-4A29-9A65-F09A9179EC26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38925" yWindow="6150" windowWidth="27045" windowHeight="14355" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Monster" sheetId="1" r:id="rId1"/>
@@ -1519,7 +1519,7 @@
         <v>61</v>
       </c>
       <c r="V9" s="3">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="W9" s="3" t="s">
         <v>62</v>
@@ -1596,7 +1596,7 @@
         <v>61</v>
       </c>
       <c r="V10" s="3">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="W10" s="3" t="s">
         <v>62</v>
@@ -1670,7 +1670,7 @@
         <v>61</v>
       </c>
       <c r="V11" s="3">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="W11" s="3" t="s">
         <v>62</v>
@@ -1747,7 +1747,7 @@
         <v>61</v>
       </c>
       <c r="V12" s="3">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="W12" s="3" t="s">
         <v>62</v>
@@ -1824,7 +1824,7 @@
         <v>61</v>
       </c>
       <c r="V13" s="3">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="W13" s="3" t="s">
         <v>62</v>
@@ -1901,7 +1901,7 @@
         <v>61</v>
       </c>
       <c r="V14" s="3">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>62</v>
@@ -1978,7 +1978,7 @@
         <v>61</v>
       </c>
       <c r="V15" s="3">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="W15" s="3" t="s">
         <v>62</v>
@@ -2055,7 +2055,7 @@
         <v>61</v>
       </c>
       <c r="V16" s="3">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="W16" s="3" t="s">
         <v>62</v>
@@ -2132,7 +2132,7 @@
         <v>61</v>
       </c>
       <c r="V17" s="3">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="W17" s="3" t="s">
         <v>62</v>
@@ -2209,7 +2209,7 @@
         <v>61</v>
       </c>
       <c r="V18" s="3">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="W18" s="3" t="s">
         <v>62</v>
@@ -2286,7 +2286,7 @@
         <v>61</v>
       </c>
       <c r="V19" s="3">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="W19" s="3" t="s">
         <v>62</v>
@@ -2366,7 +2366,7 @@
         <v>61</v>
       </c>
       <c r="V20" s="3">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="W20" s="3" t="s">
         <v>62</v>
@@ -2446,7 +2446,7 @@
         <v>61</v>
       </c>
       <c r="V21" s="3">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="W21" s="3" t="s">
         <v>62</v>
@@ -2526,7 +2526,7 @@
         <v>61</v>
       </c>
       <c r="V22" s="3">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="W22" s="3" t="s">
         <v>62</v>
@@ -2606,7 +2606,7 @@
         <v>61</v>
       </c>
       <c r="V23" s="3">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="W23" s="3" t="s">
         <v>62</v>
@@ -2683,7 +2683,7 @@
         <v>61</v>
       </c>
       <c r="V24" s="3">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="W24" s="3" t="s">
         <v>62</v>
@@ -2763,7 +2763,7 @@
         <v>61</v>
       </c>
       <c r="V25" s="3">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="W25" s="3" t="s">
         <v>62</v>
@@ -2843,7 +2843,7 @@
         <v>61</v>
       </c>
       <c r="V26" s="3">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="W26" s="3" t="s">
         <v>62</v>

--- a/Development/Common/GameData/Monster.xlsx
+++ b/Development/Common/GameData/Monster.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project\MMOGameServerProject\Development\Common\GameData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{637ADC47-D4BA-4A29-9A65-F09A9179EC26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5020D2F-249C-431A-BFCD-A9E23A8EA462}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38925" yWindow="6150" windowWidth="27045" windowHeight="14355" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Monster" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="131">
   <si>
     <t>데이터이름</t>
   </si>
@@ -480,6 +480,30 @@
   </si>
   <si>
     <t>AIKey</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>goblin_warrior</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>goblin_mage</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>고블린 전사</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>고블린 마법사</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Monsters/Goblin_Mage</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Monsters/Goblin_Warrior</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -943,7 +967,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AD26"/>
+  <dimension ref="A1:AD28"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.25" style="12" customWidth="1"/>
@@ -1519,7 +1543,7 @@
         <v>61</v>
       </c>
       <c r="V9" s="3">
-        <v>10000</v>
+        <v>1000</v>
       </c>
       <c r="W9" s="3" t="s">
         <v>62</v>
@@ -1596,7 +1620,7 @@
         <v>61</v>
       </c>
       <c r="V10" s="3">
-        <v>10000</v>
+        <v>1000</v>
       </c>
       <c r="W10" s="3" t="s">
         <v>62</v>
@@ -1670,7 +1694,7 @@
         <v>61</v>
       </c>
       <c r="V11" s="3">
-        <v>10000</v>
+        <v>1000</v>
       </c>
       <c r="W11" s="3" t="s">
         <v>62</v>
@@ -1747,7 +1771,7 @@
         <v>61</v>
       </c>
       <c r="V12" s="3">
-        <v>10000</v>
+        <v>1000</v>
       </c>
       <c r="W12" s="3" t="s">
         <v>62</v>
@@ -1824,7 +1848,7 @@
         <v>61</v>
       </c>
       <c r="V13" s="3">
-        <v>10000</v>
+        <v>1000</v>
       </c>
       <c r="W13" s="3" t="s">
         <v>62</v>
@@ -1901,7 +1925,7 @@
         <v>61</v>
       </c>
       <c r="V14" s="3">
-        <v>10000</v>
+        <v>1000</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>62</v>
@@ -1978,7 +2002,7 @@
         <v>61</v>
       </c>
       <c r="V15" s="3">
-        <v>10000</v>
+        <v>1000</v>
       </c>
       <c r="W15" s="3" t="s">
         <v>62</v>
@@ -2055,7 +2079,7 @@
         <v>61</v>
       </c>
       <c r="V16" s="3">
-        <v>10000</v>
+        <v>1000</v>
       </c>
       <c r="W16" s="3" t="s">
         <v>62</v>
@@ -2132,7 +2156,7 @@
         <v>61</v>
       </c>
       <c r="V17" s="3">
-        <v>10000</v>
+        <v>1000</v>
       </c>
       <c r="W17" s="3" t="s">
         <v>62</v>
@@ -2209,7 +2233,7 @@
         <v>61</v>
       </c>
       <c r="V18" s="3">
-        <v>10000</v>
+        <v>1000</v>
       </c>
       <c r="W18" s="3" t="s">
         <v>62</v>
@@ -2286,7 +2310,7 @@
         <v>61</v>
       </c>
       <c r="V19" s="3">
-        <v>10000</v>
+        <v>1000</v>
       </c>
       <c r="W19" s="3" t="s">
         <v>62</v>
@@ -2366,7 +2390,7 @@
         <v>61</v>
       </c>
       <c r="V20" s="3">
-        <v>10000</v>
+        <v>1000</v>
       </c>
       <c r="W20" s="3" t="s">
         <v>62</v>
@@ -2446,7 +2470,7 @@
         <v>61</v>
       </c>
       <c r="V21" s="3">
-        <v>10000</v>
+        <v>1000</v>
       </c>
       <c r="W21" s="3" t="s">
         <v>62</v>
@@ -2526,7 +2550,7 @@
         <v>61</v>
       </c>
       <c r="V22" s="3">
-        <v>10000</v>
+        <v>1000</v>
       </c>
       <c r="W22" s="3" t="s">
         <v>62</v>
@@ -2606,7 +2630,7 @@
         <v>61</v>
       </c>
       <c r="V23" s="3">
-        <v>10000</v>
+        <v>1000</v>
       </c>
       <c r="W23" s="3" t="s">
         <v>62</v>
@@ -2683,7 +2707,7 @@
         <v>61</v>
       </c>
       <c r="V24" s="3">
-        <v>10000</v>
+        <v>1000</v>
       </c>
       <c r="W24" s="3" t="s">
         <v>62</v>
@@ -2763,7 +2787,7 @@
         <v>61</v>
       </c>
       <c r="V25" s="3">
-        <v>10000</v>
+        <v>1000</v>
       </c>
       <c r="W25" s="3" t="s">
         <v>62</v>
@@ -2843,7 +2867,7 @@
         <v>61</v>
       </c>
       <c r="V26" s="3">
-        <v>10000</v>
+        <v>1000</v>
       </c>
       <c r="W26" s="3" t="s">
         <v>62</v>
@@ -2867,6 +2891,160 @@
         <v>65</v>
       </c>
       <c r="AD26" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="2:30" x14ac:dyDescent="0.3">
+      <c r="B27" s="3">
+        <v>68</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="G27" s="3">
+        <v>21</v>
+      </c>
+      <c r="I27" s="3">
+        <v>7.7</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="L27" s="3">
+        <v>1001</v>
+      </c>
+      <c r="M27" s="3">
+        <v>9001</v>
+      </c>
+      <c r="O27" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="P27" s="3">
+        <v>5</v>
+      </c>
+      <c r="Q27" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="R27" s="3">
+        <v>10</v>
+      </c>
+      <c r="S27" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="T27" s="3">
+        <v>10</v>
+      </c>
+      <c r="U27" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="V27" s="3">
+        <v>1000</v>
+      </c>
+      <c r="W27" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="X27" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y27" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z27" s="3">
+        <v>10</v>
+      </c>
+      <c r="AA27" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="AB27" s="3">
+        <v>10</v>
+      </c>
+      <c r="AC27" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="AD27" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="2:30" x14ac:dyDescent="0.3">
+      <c r="B28" s="3">
+        <v>69</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="G28" s="3">
+        <v>21</v>
+      </c>
+      <c r="I28" s="3">
+        <v>7.7</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="L28" s="3">
+        <v>1002</v>
+      </c>
+      <c r="M28" s="3">
+        <v>9002</v>
+      </c>
+      <c r="O28" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="P28" s="3">
+        <v>5</v>
+      </c>
+      <c r="Q28" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="R28" s="3">
+        <v>10</v>
+      </c>
+      <c r="S28" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="T28" s="3">
+        <v>10</v>
+      </c>
+      <c r="U28" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="V28" s="3">
+        <v>1000</v>
+      </c>
+      <c r="W28" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="X28" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y28" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z28" s="3">
+        <v>10</v>
+      </c>
+      <c r="AA28" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="AB28" s="3">
+        <v>10</v>
+      </c>
+      <c r="AC28" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="AD28" s="3">
         <v>1</v>
       </c>
     </row>

--- a/Development/Common/GameData/Monster.xlsx
+++ b/Development/Common/GameData/Monster.xlsx
@@ -1,42 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project\MMOGameServerProject\Development\Common\GameData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5020D2F-249C-431A-BFCD-A9E23A8EA462}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50904760-73ED-466D-9974-4AADFD918EB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="5355" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Monster" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="136">
   <si>
     <t>데이터이름</t>
   </si>
@@ -50,7 +34,50 @@
     <t>키값</t>
   </si>
   <si>
+    <t>메모</t>
+  </si>
+  <si>
+    <t>몬스터이름</t>
+  </si>
+  <si>
+    <t>참고</t>
+  </si>
+  <si>
+    <t>프리팹</t>
+  </si>
+  <si>
+    <t>아이템드랍</t>
+  </si>
+  <si>
+    <t>경험치</t>
+  </si>
+  <si>
+    <t>몬스터 등급</t>
+  </si>
+  <si>
+    <t>몬스터AI</t>
+  </si>
+  <si>
+    <t>몬스터 스킬</t>
+  </si>
+  <si>
+    <t>기본 스탯</t>
+  </si>
+  <si>
     <t>컬럼설명세부</t>
+  </si>
+  <si>
+    <t>몬스터 관련 특징 기입
+예)</t>
+  </si>
+  <si>
+    <t>프리팹 경로. 루트경로는 Assets/Resources/ 이다.</t>
+  </si>
+  <si>
+    <t>아이템 드랍그룹 Key</t>
+  </si>
+  <si>
+    <t>해당 몬스터가 Item 드랍을 할 것인지 설정</t>
   </si>
   <si>
     <t>RewardItem 조건 불만족 시 사용함
@@ -58,6 +85,12 @@
 FALSE : 삭제</t>
   </si>
   <si>
+    <t>해당 몬스터가 경험치 지급 할 것인지 설정</t>
+  </si>
+  <si>
+    <t>SkillKey1 에는 반드시 값이 있어야 함. 목록 순서 = AI 우선순위(SelectReadySkill)</t>
+  </si>
+  <si>
     <t>Target</t>
   </si>
   <si>
@@ -67,443 +100,338 @@
     <t>none</t>
   </si>
   <si>
+    <t>client</t>
+  </si>
+  <si>
     <t>server</t>
   </si>
   <si>
     <t>DataType</t>
   </si>
   <si>
+    <t>int32</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>bool</t>
+  </si>
+  <si>
+    <t>double</t>
+  </si>
+  <si>
+    <t>enum</t>
+  </si>
+  <si>
+    <t>DataTypeDetail</t>
+  </si>
+  <si>
+    <t>MonsterGrade</t>
+  </si>
+  <si>
+    <t>Stat</t>
+  </si>
+  <si>
     <t>DefaultValue</t>
   </si>
   <si>
+    <t>Normal</t>
+  </si>
+  <si>
     <t>컬럼명</t>
   </si>
   <si>
     <t>Key</t>
   </si>
   <si>
-    <t>DataTypeDetail</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>메모</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>몬스터이름</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>참고</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <t>참고이름</t>
   </si>
   <si>
     <t>Name</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>client</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemDropGroup</t>
+  </si>
+  <si>
+    <t>IsItemDrop</t>
+  </si>
+  <si>
+    <t>Exp</t>
+  </si>
+  <si>
+    <t>IsExp</t>
+  </si>
+  <si>
+    <t>Grade</t>
+  </si>
+  <si>
+    <t>AIKey</t>
+  </si>
+  <si>
+    <t>SkillKey1</t>
+  </si>
+  <si>
+    <t>SkillKey2</t>
+  </si>
+  <si>
+    <t>SkillKey3</t>
+  </si>
+  <si>
+    <t>SkillKey4</t>
+  </si>
+  <si>
+    <t>Stat1</t>
+  </si>
+  <si>
+    <t>StatValue1</t>
+  </si>
+  <si>
+    <t>Stat2</t>
+  </si>
+  <si>
+    <t>StatValue2</t>
+  </si>
+  <si>
+    <t>Stat3</t>
+  </si>
+  <si>
+    <t>StatValue3</t>
+  </si>
+  <si>
+    <t>Stat4</t>
+  </si>
+  <si>
+    <t>StatValue4</t>
+  </si>
+  <si>
+    <t>Stat5</t>
+  </si>
+  <si>
+    <t>StatValue5</t>
+  </si>
+  <si>
+    <t>Stat6</t>
+  </si>
+  <si>
+    <t>StatValue6</t>
+  </si>
+  <si>
+    <t>Stat7</t>
+  </si>
+  <si>
+    <t>StatValue7</t>
+  </si>
+  <si>
+    <t>Stat8</t>
+  </si>
+  <si>
+    <t>StatValue8</t>
+  </si>
+  <si>
+    <t>Slime_01</t>
+  </si>
+  <si>
+    <t>슬라임</t>
+  </si>
+  <si>
+    <t>Prefabs/Monsters/Slime_01</t>
+  </si>
+  <si>
+    <t>MoveSpdAdd</t>
+  </si>
+  <si>
+    <t>StrAdd</t>
+  </si>
+  <si>
+    <t>IntAdd</t>
+  </si>
+  <si>
+    <t>HpAdd</t>
+  </si>
+  <si>
+    <t>MpAdd</t>
+  </si>
+  <si>
+    <t>PDefAdd</t>
+  </si>
+  <si>
+    <t>MDefAdd</t>
+  </si>
+  <si>
+    <t>AtkSpdAdd</t>
+  </si>
+  <si>
+    <t>Slime_01_King</t>
+  </si>
+  <si>
+    <t>킹 슬라임</t>
+  </si>
+  <si>
+    <t>Prefabs/Monsters/Slime_01_King</t>
+  </si>
+  <si>
+    <t>Slime_01_MeltalHelmet</t>
+  </si>
+  <si>
+    <t>헬멧 슬라임</t>
+  </si>
+  <si>
+    <t>Prefabs/Monsters/Slime_01_MeltalHelmet</t>
+  </si>
+  <si>
+    <t>Slime_01_Viking</t>
+  </si>
+  <si>
+    <t>바이킹 슬라임</t>
+  </si>
+  <si>
+    <t>Prefabs/Monsters/Slime_01_Viking</t>
+  </si>
+  <si>
+    <t>Slime_02</t>
+  </si>
+  <si>
+    <t>Prefabs/Monsters/Slime_02</t>
+  </si>
+  <si>
+    <t>Slime_03</t>
+  </si>
+  <si>
+    <t>Prefabs/Monsters/Slime_03</t>
+  </si>
+  <si>
+    <t>Slime_03 King</t>
+  </si>
+  <si>
+    <t>Prefabs/Monsters/Slime_03 King</t>
+  </si>
+  <si>
+    <t>Slime_03 Leaf</t>
+  </si>
+  <si>
+    <t>리프 슬라임</t>
+  </si>
+  <si>
+    <t>Prefabs/Monsters/Slime_03 Leaf</t>
+  </si>
+  <si>
+    <t>Slime_03 Sprout</t>
+  </si>
+  <si>
+    <t>새싹 슬라임</t>
+  </si>
+  <si>
+    <t>Prefabs/Monsters/Slime_03 Sprout</t>
+  </si>
+  <si>
+    <t>Slime_01_big</t>
+  </si>
+  <si>
+    <t>거대 슬라임</t>
+  </si>
+  <si>
+    <t>Prefabs/Monsters/Slime_01_big</t>
+  </si>
+  <si>
+    <t>Slime_01_King_big</t>
+  </si>
+  <si>
+    <t>거대 킹 슬라임</t>
+  </si>
+  <si>
+    <t>Prefabs/Monsters/Slime_01_King_big</t>
+  </si>
+  <si>
+    <t>Slime_01_MeltalHelmet_big</t>
+  </si>
+  <si>
+    <t>거대 헬멧 슬라임</t>
+  </si>
+  <si>
+    <t>Prefabs/Monsters/Slime_01_MeltalHelmet_big</t>
+  </si>
+  <si>
+    <t>Slime_01_Viking_big</t>
+  </si>
+  <si>
+    <t>거대 바이킹 슬라임</t>
+  </si>
+  <si>
+    <t>Prefabs/Monsters/Slime_01_Viking_big</t>
+  </si>
+  <si>
+    <t>Slime_02_big</t>
+  </si>
+  <si>
+    <t>Prefabs/Monsters/Slime_02_big</t>
+  </si>
+  <si>
+    <t>Slime_03_big</t>
+  </si>
+  <si>
+    <t>Prefabs/Monsters/Slime_03_big</t>
+  </si>
+  <si>
+    <t>Slime_03 King_big</t>
+  </si>
+  <si>
+    <t>Prefabs/Monsters/Slime_03 King_big</t>
+  </si>
+  <si>
+    <t>Slime_03 Leaf_big</t>
+  </si>
+  <si>
+    <t>거대 리프 슬라임</t>
+  </si>
+  <si>
+    <t>Prefabs/Monsters/Slime_03 Leaf_big</t>
+  </si>
+  <si>
+    <t>Slime_03 Sprout_big</t>
+  </si>
+  <si>
+    <t>거대 새싹 슬라임</t>
+  </si>
+  <si>
+    <t>Prefabs/Monsters/Slime_03 Sprout_big</t>
+  </si>
+  <si>
+    <t>goblin_warrior</t>
+  </si>
+  <si>
+    <t>고블린 전사</t>
+  </si>
+  <si>
+    <t>Prefabs/Monsters/Goblin_Warrior</t>
+  </si>
+  <si>
+    <t>goblin_mage</t>
+  </si>
+  <si>
+    <t>고블린 마법사</t>
+  </si>
+  <si>
+    <t>Prefabs/Monsters/Goblin_Mage</t>
+  </si>
+  <si>
+    <t>DragonUsurper_Red</t>
+  </si>
+  <si>
+    <t>찬탈자 드래곤</t>
+  </si>
+  <si>
+    <t>Prefabs/Monsters/Dragon_Usurper_Red</t>
+  </si>
+  <si>
+    <t>Boss</t>
   </si>
   <si>
     <t>all</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>server</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>아이템드랍</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ItemDropGroup</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>아이템 드랍그룹 Key</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>해당 몬스터가 Item 드랍을 할 것인지 설정</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>bool</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>경험치</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>IsItemDrop</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>해당 몬스터가 경험치 지급 할 것인지 설정</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Exp</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>IsExp</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>enum</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>MonsterGrade</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Grade</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>몬스터 등급</t>
-  </si>
-  <si>
-    <t>Normal</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>double</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Stat1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Stat2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Stat3</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>StatValue1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>StatValue2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>StatValue3</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Stat</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>참고이름</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 스탯</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Stat4</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>StatValue4</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Stat5</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>StatValue5</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Stat6</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>StatValue6</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Stat7</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>StatValue7</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Stat8</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>StatValue8</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>StrAdd</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>IntAdd</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>MoveSpdAdd</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>HpAdd</t>
-  </si>
-  <si>
-    <t>MpAdd</t>
-  </si>
-  <si>
-    <t>PDefAdd</t>
-  </si>
-  <si>
-    <t>MDefAdd</t>
-  </si>
-  <si>
-    <t>AtkSpdAdd</t>
-  </si>
-  <si>
-    <t>몬스터 관련 특징 기입
-예)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>프리팹</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>PrefabPath</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>프리팹 경로. 루트경로는 Assets/Resources/ 이다.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Slime_01_King</t>
-  </si>
-  <si>
-    <t>Slime_01_MeltalHelmet</t>
-  </si>
-  <si>
-    <t>Slime_01_Viking</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Slime_02</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Slime_03</t>
-  </si>
-  <si>
-    <t>Slime_03 King</t>
-  </si>
-  <si>
-    <t>Slime_03 Leaf</t>
-  </si>
-  <si>
-    <t>슬라임</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>킹 슬라임</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>헬멧 슬라임</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>바이킹 슬라임</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>리프 슬라임</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Slime_03 Sprout</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>새싹 슬라임</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Slime_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/Monsters/Slime_01</t>
-  </si>
-  <si>
-    <t>Prefabs/Monsters/Slime_01_King</t>
-  </si>
-  <si>
-    <t>Prefabs/Monsters/Slime_01_MeltalHelmet</t>
-  </si>
-  <si>
-    <t>Prefabs/Monsters/Slime_01_Viking</t>
-  </si>
-  <si>
-    <t>Prefabs/Monsters/Slime_02</t>
-  </si>
-  <si>
-    <t>Prefabs/Monsters/Slime_03</t>
-  </si>
-  <si>
-    <t>Prefabs/Monsters/Slime_03 King</t>
-  </si>
-  <si>
-    <t>Prefabs/Monsters/Slime_03 Leaf</t>
-  </si>
-  <si>
-    <t>Prefabs/Monsters/Slime_03 Sprout</t>
-  </si>
-  <si>
-    <t>Slime_01_big</t>
-  </si>
-  <si>
-    <t>거대 슬라임</t>
-  </si>
-  <si>
-    <t>Prefabs/Monsters/Slime_01_big</t>
-  </si>
-  <si>
-    <t>Slime_01_King_big</t>
-  </si>
-  <si>
-    <t>거대 킹 슬라임</t>
-  </si>
-  <si>
-    <t>Prefabs/Monsters/Slime_01_King_big</t>
-  </si>
-  <si>
-    <t>Slime_01_MeltalHelmet_big</t>
-  </si>
-  <si>
-    <t>거대 헬멧 슬라임</t>
-  </si>
-  <si>
-    <t>Prefabs/Monsters/Slime_01_MeltalHelmet_big</t>
-  </si>
-  <si>
-    <t>Slime_01_Viking_big</t>
-  </si>
-  <si>
-    <t>거대 바이킹 슬라임</t>
-  </si>
-  <si>
-    <t>Prefabs/Monsters/Slime_01_Viking_big</t>
-  </si>
-  <si>
-    <t>Slime_02_big</t>
-  </si>
-  <si>
-    <t>Prefabs/Monsters/Slime_02_big</t>
-  </si>
-  <si>
-    <t>Slime_03_big</t>
-  </si>
-  <si>
-    <t>Prefabs/Monsters/Slime_03_big</t>
-  </si>
-  <si>
-    <t>Slime_03 King_big</t>
-  </si>
-  <si>
-    <t>Prefabs/Monsters/Slime_03 King_big</t>
-  </si>
-  <si>
-    <t>Slime_03 Leaf_big</t>
-  </si>
-  <si>
-    <t>거대 리프 슬라임</t>
-  </si>
-  <si>
-    <t>Prefabs/Monsters/Slime_03 Leaf_big</t>
-  </si>
-  <si>
-    <t>Slime_03 Sprout_big</t>
-  </si>
-  <si>
-    <t>거대 새싹 슬라임</t>
-  </si>
-  <si>
-    <t>Prefabs/Monsters/Slime_03 Sprout_big</t>
-  </si>
-  <si>
-    <t>int32</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillKey1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillKey2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>몬스터 스킬</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillKey1 에는 반드시 값이 있어야 함</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>몬스터AI</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>AIKey</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>goblin_warrior</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>goblin_mage</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>고블린 전사</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>고블린 마법사</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/Monsters/Goblin_Mage</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/Monsters/Goblin_Warrior</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -640,10 +568,10 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -967,7 +895,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AD28"/>
+  <dimension ref="A1:AF29"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.25" style="12" customWidth="1"/>
@@ -986,10 +914,11 @@
     <col min="18" max="18" width="16.375" style="3" customWidth="1"/>
     <col min="19" max="19" width="15.625" style="3" customWidth="1"/>
     <col min="20" max="20" width="16.25" style="3" customWidth="1"/>
-    <col min="21" max="16384" width="9" style="3"/>
+    <col min="21" max="21" width="9" style="3" customWidth="1"/>
+    <col min="22" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -997,7 +926,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1005,40 +934,40 @@
         <v>3</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>67</v>
+        <v>7</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="H2" s="4"/>
       <c r="I2" s="4" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="J2" s="4"/>
       <c r="K2" s="4" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>123</v>
+        <v>11</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>121</v>
+        <v>12</v>
       </c>
       <c r="N2" s="4"/>
-      <c r="O2" s="4" t="s">
-        <v>47</v>
-      </c>
+      <c r="O2" s="4"/>
       <c r="P2" s="4"/>
-      <c r="Q2" s="4"/>
+      <c r="Q2" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="R2" s="4"/>
       <c r="S2" s="4"/>
       <c r="T2" s="4"/>
@@ -1052,36 +981,38 @@
       <c r="AB2" s="4"/>
       <c r="AC2" s="4"/>
       <c r="AD2" s="4"/>
+      <c r="AE2" s="4"/>
+      <c r="AF2" s="4"/>
     </row>
-    <row r="3" spans="1:30" s="7" customFormat="1" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:32" s="7" customFormat="1" ht="82.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
       <c r="E3" s="6" t="s">
-        <v>66</v>
+        <v>15</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>69</v>
+        <v>16</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="K3" s="6"/>
       <c r="L3" s="6"/>
       <c r="M3" s="6" t="s">
-        <v>122</v>
+        <v>21</v>
       </c>
       <c r="N3" s="6"/>
       <c r="O3" s="6"/>
@@ -1100,190 +1031,204 @@
       <c r="AB3" s="6"/>
       <c r="AC3" s="6"/>
       <c r="AD3" s="6"/>
+      <c r="AE3" s="6"/>
+      <c r="AF3" s="6"/>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>7</v>
+        <v>134</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M4" s="8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="N4" s="8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="O4" s="8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="P4" s="8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="Q4" s="8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="R4" s="8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="S4" s="8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="T4" s="8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="U4" s="8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="V4" s="8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="W4" s="8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="X4" s="8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="Y4" s="8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="Z4" s="8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AA4" s="8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AB4" s="8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AC4" s="8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AD4" s="8" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="AE4" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="AF4" s="8" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>118</v>
+        <v>28</v>
       </c>
       <c r="C5" s="8"/>
       <c r="D5" s="8" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E5" s="8"/>
       <c r="F5" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="K5" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G5" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="J5" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="K5" s="8" t="s">
+      <c r="L5" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="M5" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="N5" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="O5" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="P5" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q5" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="R5" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="S5" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="T5" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="U5" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="V5" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="W5" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="X5" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="Y5" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z5" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="AA5" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB5" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC5" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD5" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="AE5" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF5" s="8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="L5" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="M5" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="N5" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="O5" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="P5" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q5" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="R5" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="S5" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="T5" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="U5" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="V5" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="W5" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="X5" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y5" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z5" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="AA5" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="AB5" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="AC5" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="AD5" s="8" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>14</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -1300,42 +1245,44 @@
       <c r="L6" s="8"/>
       <c r="M6" s="8"/>
       <c r="N6" s="8"/>
-      <c r="O6" s="8" t="s">
-        <v>45</v>
-      </c>
+      <c r="O6" s="8"/>
       <c r="P6" s="8"/>
       <c r="Q6" s="8" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="R6" s="8"/>
       <c r="S6" s="8" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="T6" s="8"/>
       <c r="U6" s="8" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="V6" s="8"/>
       <c r="W6" s="8" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="X6" s="8"/>
       <c r="Y6" s="8" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="Z6" s="8"/>
       <c r="AA6" s="8" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="AB6" s="8"/>
       <c r="AC6" s="8" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="AD6" s="8"/>
+      <c r="AE6" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="AF6" s="8"/>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="B7" s="8">
         <v>0</v>
@@ -1368,7 +1315,9 @@
       <c r="N7" s="8">
         <v>0</v>
       </c>
-      <c r="O7" s="8"/>
+      <c r="O7" s="8">
+        <v>0</v>
+      </c>
       <c r="P7" s="8">
         <v>0</v>
       </c>
@@ -1400,111 +1349,121 @@
       <c r="AD7" s="8">
         <v>0</v>
       </c>
+      <c r="AE7" s="8"/>
+      <c r="AF7" s="8">
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="1:30" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:32" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C8" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="I8" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="J8" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="K8" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="D8" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="G8" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="H8" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="I8" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="J8" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K8" s="10" t="s">
-        <v>35</v>
-      </c>
       <c r="L8" s="10" t="s">
-        <v>124</v>
+        <v>47</v>
       </c>
       <c r="M8" s="10" t="s">
-        <v>119</v>
+        <v>48</v>
       </c>
       <c r="N8" s="10" t="s">
-        <v>120</v>
+        <v>49</v>
       </c>
       <c r="O8" s="10" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="P8" s="10" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="Q8" s="10" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="R8" s="10" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="S8" s="10" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="T8" s="10" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="U8" s="10" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="V8" s="10" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="W8" s="10" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="X8" s="10" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="Y8" s="10" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="Z8" s="10" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="AA8" s="10" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="AB8" s="10" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="AC8" s="10" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="AD8" s="10" t="s">
-        <v>57</v>
+        <v>65</v>
+      </c>
+      <c r="AE8" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF8" s="10" t="s">
+        <v>67</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B9" s="3">
         <v>50</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="G9" s="3">
         <v>301</v>
@@ -1521,67 +1480,67 @@
       <c r="M9" s="3">
         <v>9002</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="R9" s="3">
         <v>5</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="R9" s="3">
-        <v>10</v>
-      </c>
       <c r="S9" s="3" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="T9" s="3">
         <v>10</v>
       </c>
       <c r="U9" s="3" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="V9" s="3">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="W9" s="3" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="X9" s="3">
+        <v>200</v>
+      </c>
+      <c r="Y9" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z9" s="3">
         <v>100</v>
       </c>
-      <c r="Y9" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="Z9" s="3">
-        <v>10</v>
-      </c>
       <c r="AA9" s="3" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="AB9" s="3">
         <v>10</v>
       </c>
       <c r="AC9" s="3" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="AD9" s="3">
+        <v>10</v>
+      </c>
+      <c r="AE9" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AF9" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B10" s="3">
         <v>51</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="G10" s="3">
         <v>21</v>
@@ -1598,67 +1557,67 @@
       <c r="M10" s="3">
         <v>9001</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="R10" s="3">
         <v>5</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="R10" s="3">
-        <v>10</v>
-      </c>
       <c r="S10" s="3" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="T10" s="3">
         <v>10</v>
       </c>
       <c r="U10" s="3" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="V10" s="3">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="W10" s="3" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="X10" s="3">
+        <v>200</v>
+      </c>
+      <c r="Y10" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z10" s="3">
         <v>100</v>
       </c>
-      <c r="Y10" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="Z10" s="3">
-        <v>10</v>
-      </c>
       <c r="AA10" s="3" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="AB10" s="3">
         <v>10</v>
       </c>
       <c r="AC10" s="3" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="AD10" s="3">
+        <v>10</v>
+      </c>
+      <c r="AE10" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AF10" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B11" s="3">
         <v>52</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="G11" s="3">
         <v>21</v>
@@ -1672,67 +1631,67 @@
       <c r="M11" s="3">
         <v>9001</v>
       </c>
-      <c r="O11" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="P11" s="3">
+      <c r="Q11" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="R11" s="3">
         <v>5</v>
       </c>
-      <c r="Q11" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="R11" s="3">
-        <v>10</v>
-      </c>
       <c r="S11" s="3" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="T11" s="3">
         <v>10</v>
       </c>
       <c r="U11" s="3" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="V11" s="3">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="W11" s="3" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="X11" s="3">
+        <v>200</v>
+      </c>
+      <c r="Y11" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z11" s="3">
         <v>100</v>
       </c>
-      <c r="Y11" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="Z11" s="3">
-        <v>10</v>
-      </c>
       <c r="AA11" s="3" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="AB11" s="3">
         <v>10</v>
       </c>
       <c r="AC11" s="3" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="AD11" s="3">
+        <v>10</v>
+      </c>
+      <c r="AE11" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AF11" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B12" s="3">
         <v>53</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G12" s="3">
         <v>301</v>
@@ -1749,64 +1708,64 @@
       <c r="M12" s="3">
         <v>9001</v>
       </c>
-      <c r="O12" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="R12" s="3">
         <v>5</v>
       </c>
-      <c r="Q12" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="R12" s="3">
-        <v>10</v>
-      </c>
       <c r="S12" s="3" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="T12" s="3">
         <v>10</v>
       </c>
       <c r="U12" s="3" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="V12" s="3">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="W12" s="3" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="X12" s="3">
+        <v>200</v>
+      </c>
+      <c r="Y12" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z12" s="3">
         <v>100</v>
       </c>
-      <c r="Y12" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="Z12" s="3">
-        <v>10</v>
-      </c>
       <c r="AA12" s="3" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="AB12" s="3">
         <v>10</v>
       </c>
       <c r="AC12" s="3" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="AD12" s="3">
+        <v>10</v>
+      </c>
+      <c r="AE12" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AF12" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B13" s="3">
         <v>54</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>89</v>
@@ -1826,67 +1785,67 @@
       <c r="M13" s="3">
         <v>9001</v>
       </c>
-      <c r="O13" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="P13" s="3">
+      <c r="Q13" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="R13" s="3">
         <v>5</v>
       </c>
-      <c r="Q13" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="R13" s="3">
-        <v>10</v>
-      </c>
       <c r="S13" s="3" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="T13" s="3">
         <v>10</v>
       </c>
       <c r="U13" s="3" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="V13" s="3">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="W13" s="3" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="X13" s="3">
+        <v>200</v>
+      </c>
+      <c r="Y13" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z13" s="3">
         <v>100</v>
       </c>
-      <c r="Y13" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="Z13" s="3">
-        <v>10</v>
-      </c>
       <c r="AA13" s="3" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="AB13" s="3">
         <v>10</v>
       </c>
       <c r="AC13" s="3" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="AD13" s="3">
+        <v>10</v>
+      </c>
+      <c r="AE13" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AF13" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B14" s="3">
         <v>55</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G14" s="3">
         <v>21</v>
@@ -1903,67 +1862,67 @@
       <c r="M14" s="3">
         <v>9002</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="R14" s="3">
         <v>5</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="R14" s="3">
-        <v>10</v>
-      </c>
       <c r="S14" s="3" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="T14" s="3">
         <v>10</v>
       </c>
       <c r="U14" s="3" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="V14" s="3">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="W14" s="3" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="X14" s="3">
+        <v>200</v>
+      </c>
+      <c r="Y14" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z14" s="3">
         <v>100</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="Z14" s="3">
-        <v>10</v>
-      </c>
       <c r="AA14" s="3" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="AB14" s="3">
         <v>10</v>
       </c>
       <c r="AC14" s="3" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="AD14" s="3">
+        <v>10</v>
+      </c>
+      <c r="AE14" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AF14" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B15" s="3">
         <v>56</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G15" s="3">
         <v>301</v>
@@ -1980,67 +1939,67 @@
       <c r="M15" s="3">
         <v>9002</v>
       </c>
-      <c r="O15" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="R15" s="3">
         <v>5</v>
       </c>
-      <c r="Q15" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="R15" s="3">
-        <v>10</v>
-      </c>
       <c r="S15" s="3" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="T15" s="3">
         <v>10</v>
       </c>
       <c r="U15" s="3" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="V15" s="3">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="W15" s="3" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="X15" s="3">
+        <v>200</v>
+      </c>
+      <c r="Y15" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z15" s="3">
         <v>100</v>
       </c>
-      <c r="Y15" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="Z15" s="3">
-        <v>10</v>
-      </c>
       <c r="AA15" s="3" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="AB15" s="3">
         <v>10</v>
       </c>
       <c r="AC15" s="3" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="AD15" s="3">
+        <v>10</v>
+      </c>
+      <c r="AE15" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AF15" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B16" s="3">
         <v>57</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="G16" s="3">
         <v>21</v>
@@ -2057,67 +2016,67 @@
       <c r="M16" s="3">
         <v>9002</v>
       </c>
-      <c r="O16" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="P16" s="3">
+      <c r="Q16" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="R16" s="3">
         <v>5</v>
       </c>
-      <c r="Q16" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="R16" s="3">
-        <v>10</v>
-      </c>
       <c r="S16" s="3" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="T16" s="3">
         <v>10</v>
       </c>
       <c r="U16" s="3" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="V16" s="3">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="W16" s="3" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="X16" s="3">
+        <v>200</v>
+      </c>
+      <c r="Y16" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z16" s="3">
         <v>100</v>
       </c>
-      <c r="Y16" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="Z16" s="3">
-        <v>10</v>
-      </c>
       <c r="AA16" s="3" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="AB16" s="3">
         <v>10</v>
       </c>
       <c r="AC16" s="3" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="AD16" s="3">
+        <v>10</v>
+      </c>
+      <c r="AE16" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AF16" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B17" s="3">
         <v>58</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="G17" s="3">
         <v>21</v>
@@ -2134,67 +2093,67 @@
       <c r="M17" s="3">
         <v>9002</v>
       </c>
-      <c r="O17" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="R17" s="3">
         <v>5</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="R17" s="3">
-        <v>10</v>
-      </c>
       <c r="S17" s="3" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="T17" s="3">
         <v>10</v>
       </c>
       <c r="U17" s="3" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="V17" s="3">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="W17" s="3" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="X17" s="3">
+        <v>200</v>
+      </c>
+      <c r="Y17" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z17" s="3">
         <v>100</v>
       </c>
-      <c r="Y17" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="Z17" s="3">
-        <v>10</v>
-      </c>
       <c r="AA17" s="3" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="AB17" s="3">
         <v>10</v>
       </c>
       <c r="AC17" s="3" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="AD17" s="3">
+        <v>10</v>
+      </c>
+      <c r="AE17" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AF17" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B18" s="3">
         <v>59</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="G18" s="3">
         <v>301</v>
@@ -2211,67 +2170,67 @@
       <c r="M18" s="3">
         <v>9002</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="R18" s="3">
         <v>5</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="R18" s="3">
-        <v>10</v>
-      </c>
       <c r="S18" s="3" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="T18" s="3">
         <v>10</v>
       </c>
       <c r="U18" s="3" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="V18" s="3">
+        <v>10</v>
+      </c>
+      <c r="W18" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="X18" s="3">
         <v>1000</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z18" s="3">
         <v>100</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="Z18" s="3">
-        <v>10</v>
-      </c>
       <c r="AA18" s="3" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="AB18" s="3">
         <v>10</v>
       </c>
       <c r="AC18" s="3" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="AD18" s="3">
+        <v>10</v>
+      </c>
+      <c r="AE18" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AF18" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B19" s="3">
         <v>60</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="G19" s="3">
         <v>21</v>
@@ -2288,67 +2247,67 @@
       <c r="M19" s="3">
         <v>9001</v>
       </c>
-      <c r="O19" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="P19" s="3">
+      <c r="Q19" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="R19" s="3">
         <v>5</v>
       </c>
-      <c r="Q19" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="R19" s="3">
-        <v>10</v>
-      </c>
       <c r="S19" s="3" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="T19" s="3">
         <v>10</v>
       </c>
       <c r="U19" s="3" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="V19" s="3">
+        <v>10</v>
+      </c>
+      <c r="W19" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="X19" s="3">
         <v>1000</v>
       </c>
-      <c r="W19" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="X19" s="3">
+      <c r="Y19" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z19" s="3">
         <v>100</v>
       </c>
-      <c r="Y19" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="Z19" s="3">
-        <v>10</v>
-      </c>
       <c r="AA19" s="3" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="AB19" s="3">
         <v>10</v>
       </c>
       <c r="AC19" s="3" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="AD19" s="3">
+        <v>10</v>
+      </c>
+      <c r="AE19" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AF19" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B20" s="3">
         <v>61</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="G20" s="3">
         <v>21</v>
@@ -2363,72 +2322,69 @@
         <v>1002</v>
       </c>
       <c r="M20" s="3">
-        <v>9002</v>
-      </c>
-      <c r="N20" s="3">
         <v>9001</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="R20" s="3">
         <v>5</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="R20" s="3">
-        <v>10</v>
-      </c>
       <c r="S20" s="3" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="T20" s="3">
         <v>10</v>
       </c>
       <c r="U20" s="3" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="V20" s="3">
+        <v>10</v>
+      </c>
+      <c r="W20" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="X20" s="3">
         <v>1000</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z20" s="3">
         <v>100</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>10</v>
-      </c>
       <c r="AA20" s="3" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="AB20" s="3">
         <v>10</v>
       </c>
       <c r="AC20" s="3" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="AD20" s="3">
+        <v>10</v>
+      </c>
+      <c r="AE20" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AF20" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B21" s="3">
         <v>62</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="G21" s="3">
         <v>301</v>
@@ -2443,72 +2399,69 @@
         <v>1002</v>
       </c>
       <c r="M21" s="3">
-        <v>9002</v>
-      </c>
-      <c r="N21" s="3">
         <v>9001</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="R21" s="3">
         <v>5</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="R21" s="3">
-        <v>10</v>
-      </c>
       <c r="S21" s="3" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="T21" s="3">
         <v>10</v>
       </c>
       <c r="U21" s="3" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="V21" s="3">
+        <v>10</v>
+      </c>
+      <c r="W21" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="X21" s="3">
         <v>1000</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z21" s="3">
         <v>100</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="Z21" s="3">
-        <v>10</v>
-      </c>
       <c r="AA21" s="3" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="AB21" s="3">
         <v>10</v>
       </c>
       <c r="AC21" s="3" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="AD21" s="3">
+        <v>10</v>
+      </c>
+      <c r="AE21" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AF21" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B22" s="3">
         <v>63</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="G22" s="3">
         <v>21</v>
@@ -2523,72 +2476,69 @@
         <v>1002</v>
       </c>
       <c r="M22" s="3">
-        <v>9002</v>
-      </c>
-      <c r="N22" s="3">
         <v>9001</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="R22" s="3">
         <v>5</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="R22" s="3">
-        <v>10</v>
-      </c>
       <c r="S22" s="3" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="T22" s="3">
         <v>10</v>
       </c>
       <c r="U22" s="3" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="V22" s="3">
+        <v>10</v>
+      </c>
+      <c r="W22" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="X22" s="3">
         <v>1000</v>
       </c>
-      <c r="W22" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z22" s="3">
         <v>100</v>
       </c>
-      <c r="Y22" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="Z22" s="3">
-        <v>10</v>
-      </c>
       <c r="AA22" s="3" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="AB22" s="3">
         <v>10</v>
       </c>
       <c r="AC22" s="3" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="AD22" s="3">
+        <v>10</v>
+      </c>
+      <c r="AE22" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AF22" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B23" s="3">
         <v>64</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="G23" s="3">
         <v>21</v>
@@ -2603,72 +2553,69 @@
         <v>1002</v>
       </c>
       <c r="M23" s="3">
-        <v>9002</v>
-      </c>
-      <c r="N23" s="3">
         <v>9001</v>
       </c>
-      <c r="O23" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="R23" s="3">
         <v>5</v>
       </c>
-      <c r="Q23" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="R23" s="3">
-        <v>10</v>
-      </c>
       <c r="S23" s="3" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="T23" s="3">
         <v>10</v>
       </c>
       <c r="U23" s="3" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="V23" s="3">
+        <v>10</v>
+      </c>
+      <c r="W23" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="X23" s="3">
         <v>1000</v>
       </c>
-      <c r="W23" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z23" s="3">
         <v>100</v>
       </c>
-      <c r="Y23" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="Z23" s="3">
-        <v>10</v>
-      </c>
       <c r="AA23" s="3" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="AB23" s="3">
         <v>10</v>
       </c>
       <c r="AC23" s="3" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="AD23" s="3">
+        <v>10</v>
+      </c>
+      <c r="AE23" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AF23" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B24" s="3">
         <v>65</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="G24" s="3">
         <v>301</v>
@@ -2685,67 +2632,67 @@
       <c r="M24" s="3">
         <v>9001</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="R24" s="3">
         <v>5</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="R24" s="3">
-        <v>10</v>
-      </c>
       <c r="S24" s="3" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="T24" s="3">
         <v>10</v>
       </c>
       <c r="U24" s="3" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="V24" s="3">
+        <v>10</v>
+      </c>
+      <c r="W24" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="X24" s="3">
         <v>1000</v>
       </c>
-      <c r="W24" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z24" s="3">
         <v>100</v>
       </c>
-      <c r="Y24" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="Z24" s="3">
-        <v>10</v>
-      </c>
       <c r="AA24" s="3" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="AB24" s="3">
         <v>10</v>
       </c>
       <c r="AC24" s="3" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="AD24" s="3">
+        <v>10</v>
+      </c>
+      <c r="AE24" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AF24" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B25" s="3">
         <v>66</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="G25" s="3">
         <v>21</v>
@@ -2760,72 +2707,69 @@
         <v>1002</v>
       </c>
       <c r="M25" s="3">
-        <v>9002</v>
-      </c>
-      <c r="N25" s="3">
         <v>9001</v>
       </c>
-      <c r="O25" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="P25" s="3">
+      <c r="Q25" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="R25" s="3">
         <v>5</v>
       </c>
-      <c r="Q25" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="R25" s="3">
-        <v>10</v>
-      </c>
       <c r="S25" s="3" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="T25" s="3">
         <v>10</v>
       </c>
       <c r="U25" s="3" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="V25" s="3">
+        <v>10</v>
+      </c>
+      <c r="W25" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="X25" s="3">
         <v>1000</v>
       </c>
-      <c r="W25" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="X25" s="3">
+      <c r="Y25" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z25" s="3">
         <v>100</v>
       </c>
-      <c r="Y25" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="Z25" s="3">
-        <v>10</v>
-      </c>
       <c r="AA25" s="3" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="AB25" s="3">
         <v>10</v>
       </c>
       <c r="AC25" s="3" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="AD25" s="3">
+        <v>10</v>
+      </c>
+      <c r="AE25" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AF25" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B26" s="3">
         <v>67</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="G26" s="3">
         <v>21</v>
@@ -2840,72 +2784,69 @@
         <v>1002</v>
       </c>
       <c r="M26" s="3">
-        <v>9002</v>
-      </c>
-      <c r="N26" s="3">
         <v>9001</v>
       </c>
-      <c r="O26" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="R26" s="3">
         <v>5</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="R26" s="3">
-        <v>10</v>
-      </c>
       <c r="S26" s="3" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="T26" s="3">
         <v>10</v>
       </c>
       <c r="U26" s="3" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="V26" s="3">
+        <v>10</v>
+      </c>
+      <c r="W26" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="X26" s="3">
         <v>1000</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z26" s="3">
         <v>100</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="Z26" s="3">
-        <v>10</v>
-      </c>
       <c r="AA26" s="3" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="AB26" s="3">
         <v>10</v>
       </c>
       <c r="AC26" s="3" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="AD26" s="3">
+        <v>10</v>
+      </c>
+      <c r="AE26" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AF26" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B27" s="3">
         <v>68</v>
       </c>
       <c r="C27" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D27" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>127</v>
-      </c>
       <c r="F27" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="G27" s="3">
         <v>21</v>
@@ -2922,61 +2863,61 @@
       <c r="M27" s="3">
         <v>9001</v>
       </c>
-      <c r="O27" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="R27" s="3">
         <v>5</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="R27" s="3">
-        <v>10</v>
-      </c>
       <c r="S27" s="3" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="T27" s="3">
         <v>10</v>
       </c>
       <c r="U27" s="3" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="V27" s="3">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="W27" s="3" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="X27" s="3">
+        <v>400</v>
+      </c>
+      <c r="Y27" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z27" s="3">
         <v>100</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="Z27" s="3">
-        <v>10</v>
-      </c>
       <c r="AA27" s="3" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="AB27" s="3">
         <v>10</v>
       </c>
       <c r="AC27" s="3" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="AD27" s="3">
+        <v>10</v>
+      </c>
+      <c r="AE27" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AF27" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B28" s="3">
         <v>69</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>128</v>
@@ -2999,52 +2940,144 @@
       <c r="M28" s="3">
         <v>9002</v>
       </c>
-      <c r="O28" s="3" t="s">
+      <c r="Q28" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="R28" s="3">
+        <v>5</v>
+      </c>
+      <c r="S28" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="T28" s="3">
+        <v>10</v>
+      </c>
+      <c r="U28" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="V28" s="3">
+        <v>10</v>
+      </c>
+      <c r="W28" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="X28" s="3">
+        <v>400</v>
+      </c>
+      <c r="Y28" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z28" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA28" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB28" s="3">
+        <v>10</v>
+      </c>
+      <c r="AC28" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AD28" s="3">
+        <v>10</v>
+      </c>
+      <c r="AE28" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AF28" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="B29" s="3">
+        <v>70</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="G29" s="3">
+        <v>21</v>
+      </c>
+      <c r="H29" t="b">
+        <v>1</v>
+      </c>
+      <c r="I29" s="3">
+        <v>100</v>
+      </c>
+      <c r="J29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="L29" s="3">
+        <v>1003</v>
+      </c>
+      <c r="M29" s="3">
+        <v>9104</v>
+      </c>
+      <c r="N29">
+        <v>9103</v>
+      </c>
+      <c r="O29">
+        <v>9102</v>
+      </c>
+      <c r="P29">
+        <v>9101</v>
+      </c>
+      <c r="Q29" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="R29" s="3">
+        <v>4</v>
+      </c>
+      <c r="S29" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="T29" s="3">
         <v>60</v>
       </c>
-      <c r="P28" s="3">
-        <v>5</v>
-      </c>
-      <c r="Q28" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="R28" s="3">
-        <v>10</v>
-      </c>
-      <c r="S28" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="T28" s="3">
-        <v>10</v>
-      </c>
-      <c r="U28" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="V28" s="3">
-        <v>1000</v>
-      </c>
-      <c r="W28" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="X28" s="3">
-        <v>100</v>
-      </c>
-      <c r="Y28" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="Z28" s="3">
-        <v>10</v>
-      </c>
-      <c r="AA28" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="AB28" s="3">
-        <v>10</v>
-      </c>
-      <c r="AC28" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="AD28" s="3">
+      <c r="U29" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="V29" s="3">
+        <v>40</v>
+      </c>
+      <c r="W29" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="X29" s="3">
+        <v>30000</v>
+      </c>
+      <c r="Y29" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z29" s="3">
+        <v>500</v>
+      </c>
+      <c r="AA29" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB29" s="3">
+        <v>60</v>
+      </c>
+      <c r="AC29" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AD29" s="3">
+        <v>50</v>
+      </c>
+      <c r="AE29" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AF29" s="3">
         <v>1</v>
       </c>
     </row>

--- a/Development/Common/GameData/Monster.xlsx
+++ b/Development/Common/GameData/Monster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project\MMOGameServerProject\Development\Common\GameData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50904760-73ED-466D-9974-4AADFD918EB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A089920-E0E5-41B4-B0FA-E0CC65CECE34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="5355" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Monster" sheetId="1" r:id="rId1"/>
@@ -915,7 +915,9 @@
     <col min="19" max="19" width="15.625" style="3" customWidth="1"/>
     <col min="20" max="20" width="16.25" style="3" customWidth="1"/>
     <col min="21" max="21" width="9" style="3" customWidth="1"/>
-    <col min="22" max="16384" width="9" style="3"/>
+    <col min="22" max="23" width="9" style="3"/>
+    <col min="24" max="24" width="9.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:32" x14ac:dyDescent="0.3">
@@ -3042,19 +3044,19 @@
         <v>72</v>
       </c>
       <c r="T29" s="3">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>73</v>
       </c>
       <c r="V29" s="3">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>74</v>
       </c>
       <c r="X29" s="3">
-        <v>30000</v>
+        <v>10000000</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>75</v>

--- a/Development/Common/GameData/Monster.xlsx
+++ b/Development/Common/GameData/Monster.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project\MMOGameServerProject\Development\Common\GameData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A089920-E0E5-41B4-B0FA-E0CC65CECE34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12006045-8B3D-4390-A515-74A77A0BCAF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -418,9 +418,6 @@
     <t>DragonUsurper_Red</t>
   </si>
   <si>
-    <t>찬탈자 드래곤</t>
-  </si>
-  <si>
     <t>Prefabs/Monsters/Dragon_Usurper_Red</t>
   </si>
   <si>
@@ -432,6 +429,10 @@
   </si>
   <si>
     <t>PrefabPath</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>레드 드래곤</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1041,7 +1042,7 @@
         <v>22</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>24</v>
@@ -1373,7 +1374,7 @@
         <v>6</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G8" s="10" t="s">
         <v>42</v>
@@ -2999,10 +3000,10 @@
         <v>130</v>
       </c>
       <c r="D29" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="F29" s="3" t="s">
         <v>131</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>132</v>
       </c>
       <c r="G29" s="3">
         <v>21</v>
@@ -3017,7 +3018,7 @@
         <v>1</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="L29" s="3">
         <v>1003</v>
